--- a/resources/nessus/Nessus_VulnLab_scan-b.xlsx
+++ b/resources/nessus/Nessus_VulnLab_scan-b.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,10 +529,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -604,10 +602,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -679,10 +675,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -754,10 +748,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H5" t="n">
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -829,10 +821,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -904,10 +894,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H7" t="n">
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -979,10 +967,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H8" t="n">
+        <v>5432</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1054,10 +1040,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H9" t="n">
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1129,10 +1113,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H10" t="n">
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1204,10 +1186,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H11" t="n">
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1279,10 +1259,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H12" t="n">
+        <v>5432</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1354,10 +1332,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1429,10 +1405,8 @@
           <t>172.30.14.2</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H14" t="n">
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1504,10 +1478,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>27017</t>
-        </is>
+      <c r="H15" t="n">
+        <v>27017</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1579,10 +1551,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H16" t="n">
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1654,10 +1624,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H17" t="n">
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1729,10 +1697,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H18" t="n">
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1804,10 +1770,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H19" t="n">
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1879,10 +1843,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H20" t="n">
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1954,10 +1916,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H21" t="n">
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2029,10 +1989,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>27017</t>
-        </is>
+      <c r="H22" t="n">
+        <v>27017</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2104,10 +2062,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>27017</t>
-        </is>
+      <c r="H23" t="n">
+        <v>27017</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2179,10 +2135,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H24" t="n">
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2254,10 +2208,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H25" t="n">
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2329,10 +2281,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H26" t="n">
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2404,10 +2354,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>27017</t>
-        </is>
+      <c r="H27" t="n">
+        <v>27017</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2479,10 +2427,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H28" t="n">
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2554,10 +2500,8 @@
           <t>172.30.14.3</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H29" t="n">
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2629,10 +2573,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>6379</t>
-        </is>
+      <c r="H30" t="n">
+        <v>6379</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2656,7 +2598,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>['An unauthenticated INFO request to the Redis Server returned the following:', '# Server\nredis_version:4.0.14\nredis_git_sha1:00000000\nredis_git_dirty:0\nredis_build_id:165c932261a105d7\nredis_mode:standalone\nos:Linux 7.0.0-28-generic x86_64\narch_bits:64\nmultiplexing_api:epoll\natomicvar_api:atomic-builtin\ngcc_version:8.3.0\nprocess_id:1\nrun_id:cd79921e53c2f00009a27348c065f720cb63c314\ntcp_port:6379\nuptime_in_seconds:282\nuptime_in_days:0\nhz:10\nlru_clock:6465678\nexecutable:/data/redis-server\nconfig_file:', '# Clients\nconnected_clients:1\nclient_longest_output_list:0\nclient_biggest_input_buf:0\nblocked_clients:0', '# Memory\nused_memory:849232\nused_memory_human:829.33K\nused_memory_rss:3805184\nused_memory_rss_human:3.63M\nused_memory_peak:849232\nused_memory_peak_human:829.33K\nused_memory_peak_perc:107.98%\nused_memory_overhead:836126\nused_memory_startup:786488\nused_memory_dataset:13106\nused_memory_dataset_perc:20.89%\ntotal_system_memory:63588020224\ntotal_system_memory_human:59.22G\nused_memory_lua:37888\nused_memory_lua_human:37.00K\nmaxmemory:0\nmaxmemory_human:0B\nmaxmemory_policy:noeviction\nmem_fragmentation_ratio:4.48\nmem_allocator:jemalloc-4.0.3\nactive_defrag_running:0\nlazyfree_pending_objects:0', '# Persistence\nloading:0\nrdb_changes_since_last_save:0\nrdb_bgsave_in_progress:0\nrdb_last_save_time:1784850292\nrdb_last_bgsave_status:ok\nrdb_last_bgsave_time_sec:-1\nrdb_current_bgsave_time_sec:-1\nrdb_last_cow_size:0\naof_enabled:0\naof_rewrite_in_progress:0\naof_rewrite_scheduled:0\naof_last_rewrite_time_sec:-1\naof_current_rewrite_time_sec:-1\naof_last_bgrewrite_status:ok\naof_last_write_status:ok\naof_last_cow_size:0', '# Stats\ntotal_connections_received:1\ntotal_commands_processed:0\ninstantaneous_ops_per_sec:0\ntotal_net_input_bytes:5\ntotal_net_output_bytes:0\ninstantaneous_input_kbps:0.00\ninstantaneous_output_kbps:0.00\nrejected_connections:0\nsync_full:0\nsync_partial_ok:0\nsync_partial_err:0\nexpired_keys:0\nexpired_stale_perc:0.00\nexpired_time_cap_reached_count:0\nevicted_keys:0\nkeyspace_hits:0\nkeyspace_misses:0\npubsub_channels:0\npubsub_patterns:0\nlatest_fork_usec:0\nmigrate_cached_sockets:0\nslave_expires_tracked_keys:0\nactive_defrag_hits:0\nactive_defrag_misses:0\nactive_defrag_key_hits:0\nactive_defrag_key_misses:0', '# Replication\nrole:master\nconnected_slaves:0\nmaster_replid:630c5d6cd451723933068248754775ab2358c0c2\nmaster_replid2:0000000000000000000000000000000000000000\nmaster_repl_offset:0\nsecond_repl_offset:-1\nrepl_backlog_active:0\nrepl_backlog_size:1048576\nrepl_backlog_first_byte_offset:0\nrepl_backlog_histlen:0', '# CPU\nused_cpu_sys:0.14\nused_cpu_user:0.09\nused_cpu_sys_children:0.00\nused_cpu_user_children:0.00', '# Cluster\ncluster_enabled:0', '# Keyspace']</t>
+          <t>['An unauthenticated INFO request to the Redis Server returned the following:', '# Server\nredis_version:4.0.14\nredis_git_sha1:00000000\nredis_git_dirty:0\nredis_build_id:165c932261a105d7\nredis_mode:standalone\nos:Linux 7.0.0-28-generic x86_64\narch_bits:64\nmultiplexing_api:epoll\natomicvar_api:atomic-builtin\ngcc_version:8.3.0\nprocess_id:1\nrun_id:cd79921e53c2f00009a27348c065f720cb63c314\ntcp_port:6379\nuptime_in_seconds:282\nuptime_in_days:0\nhz:10\nlru_clock:6465678\nexecutable:/data/redis-server\nconfig_file:', '# Clients\nconnected_clients:1\nclient_longest_output_list:0\nclient_biggest_input_buf:0\nblocked_clients:0', '# Memory\nused_memory:849232\nused_memory_human:829.33K\nused_memory_rss:3805184\nused_memory_rss_human:3.63M\nused_memory_peak:849232\nused_memory_peak_human:829.33K\nused_memory_peak_perc:107.98%\nused_memory_overhead:836126\nused_memory_startup:786488\nused_memory_dataset:13106\nused_memory_dataset_perc:20.89%\ntotal_system_memory:63588020224\ntotal_system_memory_human:59.22G\nused_memory_lua:37888\nused_memory_lua_human:37.00K\nmaxmemory:0\nmaxmemory_human:0B\nmaxmemory_policy:noeviction\nmem_fragmentation_ratio:4.48\nmem_allocator:jemalloc-4.0.3\nactive_defrag_running:0\nlazyfree_pending_objects:0', '# Persistence\nloading:0\nrdb_changes_since_last_save:0\nrdb_bgsave_in_progress:0\nrdb_last_save_time:1784850292\nrdb_last_bgsave_status:ok\nrdb_last_bgsave_time_sec:-1\nrdb_current_bgsave_time_sec:-1\nrdb_last_cow_size:0\naof_enabled:0\naof_rewrite_in_progress:0\naof_rewrite_scheduled:0\naof_last_rewrite_time_sec:-1\naof_current_rewrite_time_sec:-1\naof_last_bgrewrite_status:ok\naof_last_write_status:ok\naof_last_cow_size:0']</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2704,10 +2646,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H31" t="n">
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2779,10 +2719,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H32" t="n">
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2854,10 +2792,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2929,10 +2865,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H34" t="n">
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3004,10 +2938,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H35" t="n">
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3079,10 +3011,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H36" t="n">
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3154,10 +3084,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6379</t>
-        </is>
+      <c r="H37" t="n">
+        <v>6379</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3229,10 +3157,8 @@
           <t>172.30.14.4</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H38" t="n">
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3304,10 +3230,8 @@
           <t>172.30.14.5</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H39" t="n">
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3379,10 +3303,8 @@
           <t>172.30.14.5</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>9200</t>
-        </is>
+      <c r="H40" t="n">
+        <v>9200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3454,10 +3376,8 @@
           <t>172.30.14.5</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H41" t="n">
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3529,10 +3449,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
+      <c r="H42" t="n">
+        <v>5984</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3604,10 +3522,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
+      <c r="H43" t="n">
+        <v>5984</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3679,10 +3595,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
+      <c r="H44" t="n">
+        <v>5984</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3754,10 +3668,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
+      <c r="H45" t="n">
+        <v>5984</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3829,10 +3741,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H46" t="n">
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3904,10 +3814,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H47" t="n">
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3979,10 +3887,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
+      <c r="H48" t="n">
+        <v>5984</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4054,10 +3960,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H49" t="n">
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4129,10 +4033,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H50" t="n">
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4204,10 +4106,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H51" t="n">
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4279,10 +4179,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H52" t="n">
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4354,10 +4252,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H53" t="n">
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4429,10 +4325,8 @@
           <t>172.30.14.6</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H54" t="n">
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4504,10 +4398,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H55" t="n">
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4579,10 +4471,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H56" t="n">
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4654,10 +4544,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H57" t="n">
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4729,10 +4617,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H58" t="n">
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4804,10 +4690,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H59" t="n">
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4879,10 +4763,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="H60" t="n">
+        <v>3128</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4954,10 +4836,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5029,10 +4909,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="H62" t="n">
+        <v>3128</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5056,7 +4934,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>['Response Code : HTTP/1.1 400 Bad Request', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : no\nOptions allowed : (Not implemented)\nHeaders :', 'Server: squid/3.3.8\n  Mime-Version: 1.0\n  Date: Thu, 23 Jul 2026 23:49:39 GMT\n  Content-Type: text/html\n  Content-Length: 3152\n  X-Squid-Error: ERR_INVALID_URL 0\n  Vary: Accept-Language\n  Content-Language: en\n  X-Cache: MISS from eaea9212d73b\n  X-Cache-Lookup: NONE from eaea9212d73b:3128\n  Via: 1.1 eaea9212d73b (squid/3.3.8)\n  Connection: close', 'Response Body :', '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD HTML 4.01//EN" "http://www.w3.org/TR/html4/strict.dtd"&gt;\n&lt;html&gt;&lt;head&gt;\n&lt;meta http-equiv="Content-Type" content="text/html; charset=utf-8"&gt;\n&lt;title&gt;ERROR: The requested URL could not be retrieved&lt;/title&gt;\n&lt;style type="text/css"&gt;&lt;!-- \n /*\n Stylesheet for Squid Error pages\n Adapted from design by Free CSS Templates\n http://www.freecsstemplates.org\n Released for free under a Creative Commons Attribution 2.5 License\n*/', '/* Page basics */\n* {\nfont-family: verdana, sans-serif;\n}', 'html body {\nmargin: 0;\npadding: 0;\nbackground: #efefef;\nfont-size: 12px;\ncolor: #1e1e1e;\n}', "/* Page displayed title area */\n#titles {\nmargin-left: 15px;\npadding: 10px;\npadding-left: 100px;\nbackground: url('http://www.squid-cache.org/Artwork/SN.png') no-repeat left;\n}", '/* initial title */\n#titles h1 {\ncolor: #000000;\n}\n#titles h2 {\ncolor: #000000;\n}', '/* special event: FTP success page titles */\n#titles ftpsuccess {\nbackground-color:#00ff00;\nwidth:100%;\n}', '/* Page displayed body content area */\n#content {\npadding: 10px;\nbackground: #ffffff;\n}', '/* General text */\np {\n}', '/* error brief description */\n#error p {\n}', '/* some data which may have caused the problem */\n#data {\n}', '/* the error message received from the system or other software */\n#sysmsg {\n}', 'pre {\n    font-family:sans-serif;\n}', '/* special event: FTP / Gopher directory listing */\n#dirmsg {\n    font-family: courier;\n    color: black;\n    font-size: 10pt;\n}\n#dirlisting {\n    margin-left: 2%;\n    margin-right: 2%;\n}\n#dirlisting tr.entry td.icon,td.filename,td.size,td.date {\n    border-bottom: groove;\n}\n#dirlisting td.size {\n    width: 50px;\n    text-align: right;\n    padding-right: 5px;\n}', '/* horizontal lines */\nhr {\nmargin: 0;\n}', '/* page displayed footer area */\n#footer {\nfont-size: 9px;\npadding-left: 10px;\n}', 'body\n:lang(fa) { direction: rtl; font-size: 100%; font-family: Tahoma, Roya, sans-serif; float: right; }\n:lang(he) { direction: rtl; }\n --&gt;&lt;/style&gt;\n&lt;/head&gt;&lt;body id=ERR_INVALID_URL&gt;\n&lt;div id="titles"&gt;\n&lt;h1&gt;ERROR&lt;/h1&gt;\n&lt;h2&gt;The requested URL could not be retrieved&lt;/h2&gt;\n&lt;/div&gt;\n&lt;hr&gt;', '&lt;div id="content"&gt;\n&lt;p&gt;The following error was encountered while trying to retrieve the URL: &lt;a href="/"&gt;/&lt;/a&gt;&lt;/p&gt;', '&lt;blockquote id="error"&gt;\n&lt;p&gt;&lt;b&gt;Invalid URL&lt;/b&gt;&lt;/p&gt;\n&lt;/blockquote&gt;', '&lt;p&gt;Some aspect of the requested URL is incorrect.&lt;/p&gt;', '&lt;p&gt;Some possible problems are:&lt;/p&gt;\n&lt;ul&gt;\n&lt;li&gt;&lt;p&gt;Missing or incorrect access protocol (should be &lt;q&gt;http://&lt;/q&gt; or similar)&lt;/p&gt;&lt;/li&gt;\n&lt;li&gt;&lt;p&gt;Missing hostname&lt;/p&gt;&lt;/li&gt;\n&lt;li&gt;&lt;p&gt;Illegal double-escape in the URL-Path&lt;/p&gt;&lt;/li&gt;\n&lt;li&gt;&lt;p&gt;Illegal character in hostname; underscores are not allowed.&lt;/p&gt;&lt;/li&gt;\n&lt;/ul&gt;', '&lt;p&gt;Your cache administrator is &lt;a href="mailto:webmaster?subject=CacheErrorInfo%20-%20ERR_INVALID_URL&amp;amp;body=CacheHost%3A%20eaea9212d73b%0D%0AErrPage%3A%20ERR_INVALID_URL%0D%0AErr%3A%20%5Bnone%5D%0D%0ATimeStamp%3A%20Thu,%2023%20Jul%202026%2023%3A49%3A39%20GMT%0D%0A%0D%0AClientIP%3A%20172.30.0.2%0D%0A%0D%0AHTTP%20Request%3A%0D%0A%0D%0A%0D%0A"&gt;webmaster&lt;/a&gt;.&lt;/p&gt;\n&lt;br&gt;\n&lt;/div&gt;', '&lt;hr&gt;\n&lt;div id="footer"&gt;\n&lt;p&gt;Generated Thu, 23 Jul 2026 23:49:39 GMT by eaea9212d73b (squid/3.3.8)&lt;/p&gt;\n&lt;!-- ERR_INVALID_URL --&gt;\n&lt;/div&gt;\n&lt;/body&gt;&lt;/html&gt;']</t>
+          <t>['Response Code : HTTP/1.1 400 Bad Request', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : no\nOptions allowed : (Not implemented)\nHeaders :', 'Server: squid/3.3.8\n  Mime-Version: 1.0\n  Date: Thu, 23 Jul 2026 23:49:39 GMT\n  Content-Type: text/html\n  Content-Length: 3152\n  X-Squid-Error: ERR_INVALID_URL 0\n  Vary: Accept-Language\n  Content-Language: en\n  X-Cache: MISS from eaea9212d73b\n  X-Cache-Lookup: NONE from eaea9212d73b:3128\n  Via: 1.1 eaea9212d73b (squid/3.3.8)\n  Connection: close', 'Response Body :', '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD HTML 4.01//EN" "http://www.w3.org/TR/html4/strict.dtd"&gt;\n&lt;html&gt;&lt;head&gt;\n&lt;meta http-equiv="Content-Type" content="text/html; charset=utf-8"&gt;\n&lt;title&gt;ERROR: The requested URL could not be retrieved&lt;/title&gt;\n&lt;style type="text/css"&gt;&lt;!-- \n /*\n Stylesheet for Squid Error pages\n Adapted from design by Free CSS Templates\n http://www.freecsstemplates.org\n Released for free under a Creative Commons Attribution 2.5 License\n*/', '/* Page basics */\n* {\nfont-family: verdana, sans-serif;\n}', 'html body {\nmargin: 0;\npadding: 0;\nbackground: #efefef;\nfont-size: 12px;\ncolor: #1e1e1e;\n}', "/* Page displayed title area */\n#titles {\nmargin-left: 15px;\npadding: 10px;\npadding-left: 100px;\nbackground: url('http://www.squid-cache.org/Artwork/SN.png') no-repeat left;\n}", '/* initial title */\n#titles h1 {\ncolor: #000000;\n}\n#titles h2 {\ncolor: #000000;\n}', '/* special event: FTP success page titles */\n#titles ftpsuccess {\nbackground-color:#00ff00;\nwidth:100%;\n}', '/* Page displayed body content area */\n#content {\npadding: 10px;\nbackground: #ffffff;\n}', '/* General text */\np {\n}', '/* error brief description */\n#error p {\n}', '/* some data which may have caused the problem */\n#data {\n}', '/* the error message received from the system or other software */\n#sysmsg {\n}', 'pre {\n    font-family:sans-serif;\n}']</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -5104,10 +4982,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="H63" t="n">
+        <v>3128</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5179,10 +5055,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H64" t="n">
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5254,10 +5128,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H65" t="n">
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5329,10 +5201,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H66" t="n">
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5404,10 +5274,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="H67" t="n">
+        <v>3128</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5479,10 +5347,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="H68" t="n">
+        <v>3128</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5554,10 +5420,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H69" t="n">
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5629,10 +5493,8 @@
           <t>172.30.18.1</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H70" t="n">
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5704,10 +5566,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>5672</t>
-        </is>
+      <c r="H71" t="n">
+        <v>5672</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5779,10 +5639,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H72" t="n">
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5854,10 +5712,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H73" t="n">
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5929,10 +5785,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>5672</t>
-        </is>
+      <c r="H74" t="n">
+        <v>5672</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6004,10 +5858,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H75" t="n">
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6079,10 +5931,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H76" t="n">
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6154,10 +6004,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>4369</t>
-        </is>
+      <c r="H77" t="n">
+        <v>4369</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6229,10 +6077,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H78" t="n">
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6304,10 +6150,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H79" t="n">
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6379,10 +6223,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>4369</t>
-        </is>
+      <c r="H80" t="n">
+        <v>4369</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6454,10 +6296,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H81" t="n">
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6529,10 +6369,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H82" t="n">
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6604,10 +6442,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H83" t="n">
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6679,10 +6515,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>15672</t>
-        </is>
+      <c r="H84" t="n">
+        <v>15672</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6754,10 +6588,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H85" t="n">
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6829,10 +6661,8 @@
           <t>172.30.20.1</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H86" t="n">
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6904,10 +6734,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H87" t="n">
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6979,10 +6807,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H88" t="n">
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -7054,10 +6880,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H89" t="n">
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -7129,10 +6953,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H90" t="n">
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -7204,10 +7026,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H91" t="n">
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -7279,10 +7099,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H92" t="n">
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -7354,10 +7172,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>11211</t>
-        </is>
+      <c r="H93" t="n">
+        <v>11211</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7429,10 +7245,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H94" t="n">
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7504,10 +7318,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H95" t="n">
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7579,10 +7391,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H96" t="n">
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7654,10 +7464,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7729,10 +7537,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H98" t="n">
+        <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7804,10 +7610,8 @@
           <t>172.30.25.1</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>11211</t>
-        </is>
+      <c r="H99" t="n">
+        <v>11211</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7879,10 +7683,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H100" t="n">
+        <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7954,10 +7756,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H101" t="n">
+        <v>389</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -8029,10 +7829,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H102" t="n">
+        <v>389</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8104,10 +7902,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H103" t="n">
+        <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -8179,10 +7975,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H104" t="n">
+        <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8254,10 +8048,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H105" t="n">
+        <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -8329,10 +8121,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H106" t="n">
+        <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -8404,10 +8194,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H107" t="n">
+        <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -8479,10 +8267,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H108" t="n">
+        <v>389</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -8554,10 +8340,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H109" t="n">
+        <v>389</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -8629,10 +8413,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H110" t="n">
+        <v>389</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -8704,10 +8486,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H111" t="n">
+        <v>389</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -8779,10 +8559,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
+      <c r="H112" t="n">
+        <v>636</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -8854,10 +8632,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H113" t="n">
+        <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -8929,10 +8705,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H114" t="n">
+        <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -9004,10 +8778,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H115" t="n">
+        <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -9079,10 +8851,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H116" t="n">
+        <v>389</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -9154,10 +8924,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H117" t="n">
+        <v>389</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -9229,10 +8997,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H118" t="n">
+        <v>389</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -9256,7 +9022,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>['Subject Name:', 'Country: US\nState/Province: New Mexico\nLocality: Albuquerque\nOrganization: A1A Car Wash\nOrganization Unit: Information Technology Dep.\nCommon Name: af7ddba7e603', 'Issuer Name:', 'Country: US\nState/Province: New Mexico\nLocality: Albuquerque\nOrganization: A1A Car Wash\nOrganization Unit: Information Technology Dep.\nCommon Name: docker-light-baseimage', 'Serial Number: 00 DB 95 98 83 95 01 7F 61 20 2C B8 54 B3 C1 1A 0C 64 75 8C', 'Version: 3', 'Signature Algorithm: ECDSA With SHA-384', 'Not Valid Before: Jul 23 23:40:00 2026 GMT\nNot Valid After: Jul 23 23:40:00 2027 GMT', 'Public Key Info:', 'Algorithm: EC Public Key\nElliptic Curve: P384\nKey Length: 384 bits\nPublic Key X: 6C 45 F6 C1 F7 5C DA E2 EE DD 1E 63 B7 B9 E0 C6 60 73 81 AC \n              63 1E 82 8B E2 62 F5 A9 34 44 AF 36 49 9A 1F 4E 4D FB 50 09 \n              D1 B6 1E 89 5B 09 BC AD \nPublic Key Y: 1C 16 63 43 08 83 CF 36 5E E9 83 59 9A F0 B5 A0 E8 18 CE E8 \n              EE F9 FF 51 40 3E CA BF C7 58 E7 8A ED 21 33 3E B4 94 72 C5 \n              42 77 6B 0A 8D B1 35 32', 'Signature Length: 103 bytes / 824 bits\nSignature: 00 30 65 02 31 00 B9 1F 0D CF 74 0A 3A 15 81 7B 6E 13 ED C3 \n           E5 F5 5C 15 EC 25 F0 EE 73 AE 04 FC D2 DF E1 EE 2D 09 70 59 \n           F4 43 AF 9F DA F6 B6 B8 0F F6 9A 20 D1 7E 02 30 7A 67 B8 8C \n           DF 9F 93 B7 A7 0E F0 AE F6 FA 60 5F DE C2 CD 56 E7 FA 3E 15 \n           16 22 E2 65 0D DA 34 97 4A 21 35 04 67 6D 5F 83 AF EE 9A 6D \n           61 94 E2 3A', 'Extension: Key Usage(2.5.29.15)\nCritical: 1\nKey Usage: Digital Signature, Key Encipherment', 'Extension: Extended Key Usage(2.5.29.37)\nCritical: 0\nPurpose#1: Web Server Authentication (1.3.6.1.5.5.7.3.1)\nPurpose#2: Web Client Authentication (1.3.6.1.5.5.7.3.2)', 'Extension: Basic Constraints(2.5.29.19)\nCritical: 1', 'Extension: Subject Key Identifier(2.5.29.14)\nCritical: 0\nSubject Key Identifier: 86 2A E8 BA F5 F9 49 B9 88 70 45 43 C5 E5 E3 1B D0 5C A4 1D', 'Extension: Authority Key Identifier(2.5.29.35)\nCritical: 0\nKey Identifier: D7 12 78 64 3E D6 ED E7 B2 BD 81 71 86 36 8D 57 9C C8 14 25', 'Extension: Subject Alternative Name(2.5.29.17)\nCritical: 0\nDNS: af7ddba7e603', 'Fingerprints :', 'SHA-256 Fingerprint: 7A 79 D9 9F 49 61 7C 59 2E 28 36 B8 21 AB 90 92 ED 59 81 53 \n                     56 2B 63 C2 BA 56 83 15 07 8E 00 10 \nSHA-1 Fingerprint: A5 CA 11 0A 56 BC 3C 07 48 C1 09 76 F3 89 AC E4 20 97 AA F1 \nMD5 Fingerprint: 03 46 89 18 58 FD C2 4E 47 94 A1 CE 84 80 B0 19', 'PEM certificate :', '-----BEGIN CERTIFICATE-----\nMIIC/TCCAoOgAwIBAgIUANuVmIOVAX9hICy4VLPBGgxkdYwwCgYIKoZIzj0EAwMwgZYxCzAJBgNVBAYTAlVTMRMwEQYDVQQIEwpOZXcgTWV4aWNvMRQwEgYDVQQHEwtBbGJ1cXVlcnF1ZTEVMBMGA1UEChMMQTFBIENhciBXYXNoMSQwIgYDVQQLExtJbmZvcm1hdGlvbiBUZWNobm9sb2d5IERlcC4xHzAdBgNVBAMTFmRvY2tlci1saWdodC1iYXNlaW1hZ2UwHhcNMjYwNzIzMjM0MDAwWhcNMjcwNzIzMjM0MDAwWjCBjDELMAkGA1UEBhMCVVMxEzARBgNVBAgTCk5ldyBNZXhpY28xFDASBgNVBAcTC0FsYnVxdWVycXVlMRUwEwYDVQQKEwxBMUEgQ2FyIFdhc2gxJDAiBgNVBAsTG0luZm9ybWF0aW9uIFRlY2hub2xvZ3kgRGVwLjEVMBMGA1UEAxMMYWY3ZGRiYTdlNjAzMHYwEAYHKoZIzj0CAQYFK4EEACIDYgAEbEX2wfdc2uLu3R5jt7ngxmBzgaxjHoKL4mL1qTRErzZJmh9OTftQCdG2HolbCbytHBZjQwiDzzZe6YNZmvC1oOgYzuju+f9RQD7Kv8dY54rtITM+tJRyxUJ3awqNsTUyo4GZMIGWMA4GA1UdDwEB/wQEAwIFoDAdBgNVHSUEFjAUBggrBgEFBQcDAQYIKwYBBQUHAwIwDAYDVR0TAQH/BAIwADAdBgNVHQ4EFgQUhirouvX5SbmIcEVDxeXjG9BcpB0wHwYDVR0jBBgwFoAU1xJ4ZD7W7eeyvYFxhjaNV5zIFCUwFwYDVR0RBBAwDoIMYWY3ZGRiYTdlNjAzMAoGCCqGSM49BAMDA2gAMGUCMQC5Hw3PdAo6FYF7bhPtw+X1XBXsJfDuc64E/NLf4e4tCXBZ9EOvn9r2trgP9pog0X4CMHpnuIzfn5O3pw7wrvb6YF/ews1W5/o+FRYi4mUN2jSXSiE1BGdtX4Ov7pptYZTiOg==\n-----END CERTIFICATE-----']</t>
+          <t>['Subject Name:', 'Country: US\nState/Province: New Mexico\nLocality: Albuquerque\nOrganization: A1A Car Wash\nOrganization Unit: Information Technology Dep.\nCommon Name: af7ddba7e603', 'Issuer Name:', 'Country: US\nState/Province: New Mexico\nLocality: Albuquerque\nOrganization: A1A Car Wash\nOrganization Unit: Information Technology Dep.\nCommon Name: docker-light-baseimage', 'Serial Number: 00 DB 95 98 83 95 01 7F 61 20 2C B8 54 B3 C1 1A 0C 64 75 8C', 'Version: 3', 'Signature Algorithm: ECDSA With SHA-384', 'Not Valid Before: Jul 23 23:40:00 2026 GMT\nNot Valid After: Jul 23 23:40:00 2027 GMT', 'Public Key Info:', 'Algorithm: EC Public Key\nElliptic Curve: P384\nKey Length: 384 bits\nPublic Key X: 6C 45 F6 C1 F7 5C DA E2 EE DD 1E 63 B7 B9 E0 C6 60 73 81 AC \n              63 1E 82 8B E2 62 F5 A9 34 44 AF 36 49 9A 1F 4E 4D FB 50 09 \n              D1 B6 1E 89 5B 09 BC AD \nPublic Key Y: 1C 16 63 43 08 83 CF 36 5E E9 83 59 9A F0 B5 A0 E8 18 CE E8 \n              EE F9 FF 51 40 3E CA BF C7 58 E7 8A ED 21 33 3E B4 94 72 C5 \n              42 77 6B 0A 8D B1 35 32', 'Signature Length: 103 bytes / 824 bits\nSignature: 00 30 65 02 31 00 B9 1F 0D CF 74 0A 3A 15 81 7B 6E 13 ED C3 \n           E5 F5 5C 15 EC 25 F0 EE 73 AE 04 FC D2 DF E1 EE 2D 09 70 59 \n           F4 43 AF 9F DA F6 B6 B8 0F F6 9A 20 D1 7E 02 30 7A 67 B8 8C \n           DF 9F 93 B7 A7 0E F0 AE F6 FA 60 5F DE C2 CD 56 E7 FA 3E 15 \n           16 22 E2 65 0D DA 34 97 4A 21 35 04 67 6D 5F 83 AF EE 9A 6D \n           61 94 E2 3A', 'Extension: Key Usage(2.5.29.15)\nCritical: 1\nKey Usage: Digital Signature, Key Encipherment', 'Extension: Extended Key Usage(2.5.29.37)\nCritical: 0\nPurpose#1: Web Server Authentication (1.3.6.1.5.5.7.3.1)\nPurpose#2: Web Client Authentication (1.3.6.1.5.5.7.3.2)', 'Extension: Basic Constraints(2.5.29.19)\nCritical: 1', 'Extension: Subject Key Identifier(2.5.29.14)\nCritical: 0\nSubject Key Identifier: 86 2A E8 BA F5 F9 49 B9 88 70 45 43 C5 E5 E3 1B D0 5C A4 1D', 'Extension: Authority Key Identifier(2.5.29.35)\nCritical: 0\nKey Identifier: D7 12 78 64 3E D6 ED E7 B2 BD 81 71 86 36 8D 57 9C C8 14 25']</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -9304,10 +9070,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H119" t="n">
+        <v>389</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -9379,10 +9143,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H120" t="n">
+        <v>389</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -9454,10 +9216,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H121" t="n">
+        <v>389</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -9529,10 +9289,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H122" t="n">
+        <v>389</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9604,10 +9362,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H123" t="n">
+        <v>389</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9679,10 +9435,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H124" t="n">
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9754,10 +9508,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H125" t="n">
+        <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -9829,10 +9581,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H126" t="n">
+        <v>389</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9904,10 +9654,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="H127" t="n">
+        <v>389</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9979,10 +9727,8 @@
           <t>172.30.29.1</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H128" t="n">
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -10054,10 +9800,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
+      <c r="H129" t="n">
+        <v>8009</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -10081,7 +9825,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>['Nessus was able to exploit the issue using the following request :', '0x0000:  02 02 00 08 48 54 54 50 2F 31 2E 31 00 00 0F 2F    ....HTTP/1.1.../\n0x0010:  61 73 64 66 2F 78 78 78 78 78 2E 6A 73 70 00 00    asdf/xxxxx.jsp..\n0x0020:  09 6C 6F 63 61 6C 68 6F 73 74 00 FF FF 00 09 6C    .localhost.....l\n0x0030:  6F 63 61 6C 68 6F 73 74 00 00 50 00 00 09 A0 06    ocalhost..P.....\n0x0040:  00 0A 6B 65 65 70 2D 61 6C 69 76 65 00 00 0F 41    ..keep-alive...A\n0x0050:  63 63 65 70 74 2D 4C 61 6E 67 75 61 67 65 00 00    ccept-Language..\n0x0060:  0E 65 6E 2D 55 53 2C 65 6E 3B 71 3D 30 2E 35 00    .en-US,en;q=0.5.\n0x0070:  A0 08 00 01 30 00 00 0F 41 63 63 65 70 74 2D 45    ....0...Accept-E\n0x0080:  6E 63 6F 64 69 6E 67 00 00 13 67 7A 69 70 2C 20    ncoding...gzip, \n0x0090:  64 65 66 6C 61 74 65 2C 20 73 64 63 68 00 00 0D    deflate, sdch...\n0x00A0:  43 61 63 68 65 2D 43 6F 6E 74 72 6F 6C 00 00 09    Cache-Control...\n0x00B0:  6D 61 78 2D 61 67 65 3D 30 00 A0 0E 00 07 4D 6F    max-age=0.....Mo\n0x00C0:  7A 69 6C 6C 61 00 00 19 55 70 67 72 61 64 65 2D    zilla...Upgrade-\n0x00D0:  49 6E 73 65 63 75 72 65 2D 52 65 71 75 65 73 74    Insecure-Request\n0x00E0:  73 00 00 01 31 00 A0 01 00 09 74 65 78 74 2F 68    s...1.....text/h\n0x00F0:  74 6D 6C 00 A0 0B 00 09 6C 6F 63 61 6C 68 6F 73    tml.....localhos\n0x0100:  74 00 0A 00 21 6A 61 76 61 78 2E 73 65 72 76 6C    t...!javax.servl\n0x0110:  65 74 2E 69 6E 63 6C 75 64 65 2E 72 65 71 75 65    et.include.reque\n0x0120:  73 74 5F 75 72 69 00 00 01 31 00 0A 00 1F 6A 61    st_uri...1....ja\n0x0130:  76 61 78 2E 73 65 72 76 6C 65 74 2E 69 6E 63 6C    vax.servlet.incl\n0x0140:  75 64 65 2E 70 61 74 68 5F 69 6E 66 6F 00 00 10    ude.path_info...\n0x0150:  2F 57 45 42 2D 49 4E 46 2F 77 65 62 2E 78 6D 6C    /WEB-INF/web.xml\n0x0160:  00 0A 00 22 6A 61 76 61 78 2E 73 65 72 76 6C 65    ..."javax.servle\n0x0170:  74 2E 69 6E 63 6C 75 64 65 2E 73 65 72 76 6C 65    t.include.servle\n0x0180:  74 5F 70 61 74 68 00 00 00 00 FF                   t_path.....', 'This produced the following truncated output (limited to 10 lines) :\n------------------------------ snip ------------------------------\n..&lt;?xml version="1.0" encoding="ISO-8859-1"?&gt;\n&lt;!--\nLicensed to the Apache Software Foundation (ASF) under one or more\ncontributor license agreements.  See the NOTICE file distributed with\nthis work for additional information regarding copyright ownership.\nThe ASF licenses this file to You under the Apache License, Version 2.0\n(the "License"); you may not use this file except in compliance with\nthe License.  You may obtain a copy of the License at', 'http://www.apache.org/licenses/LICENSE-2.0\n[...]', '------------------------------ snip ------------------------------']</t>
+          <t>['Nessus was able to exploit the issue using the following request :', '0x0000:  02 02 00 08 48 54 54 50 2F 31 2E 31 00 00 0F 2F    ....HTTP/1.1.../\n0x0010:  61 73 64 66 2F 78 78 78 78 78 2E 6A 73 70 00 00    asdf/xxxxx.jsp..\n0x0020:  09 6C 6F 63 61 6C 68 6F 73 74 00 FF FF 00 09 6C    .localhost.....l\n0x0030:  6F 63 61 6C 68 6F 73 74 00 00 50 00 00 09 A0 06    ocalhost..P.....\n0x0040:  00 0A 6B 65 65 70 2D 61 6C 69 76 65 00 00 0F 41    ..keep-alive...A\n0x0050:  63 63 65 70 74 2D 4C 61 6E 67 75 61 67 65 00 00    ccept-Language..\n0x0060:  0E 65 6E 2D 55 53 2C 65 6E 3B 71 3D 30 2E 35 00    .en-US,en;q=0.5.\n0x0070:  A0 08 00 01 30 00 00 0F 41 63 63 65 70 74 2D 45    ....0...Accept-E\n0x0080:  6E 63 6F 64 69 6E 67 00 00 13 67 7A 69 70 2C 20    ncoding...gzip, \n0x0090:  64 65 66 6C 61 74 65 2C 20 73 64 63 68 00 00 0D    deflate, sdch...\n0x00A0:  43 61 63 68 65 2D 43 6F 6E 74 72 6F 6C 00 00 09    Cache-Control...\n0x00B0:  6D 61 78 2D 61 67 65 3D 30 00 A0 0E 00 07 4D 6F    max-age=0.....Mo\n0x00C0:  7A 69 6C 6C 61 00 00 19 55 70 67 72 61 64 65 2D    zilla...Upgrade-\n0x00D0:  49 6E 73 65 63 75 72 65 2D 52 65 71 75 65 73 74    Insecure-Request\n0x00E0:  73 00 00 01 31 00 A0 01 00 09 74 65 78 74 2F 68    s...1.....text/h\n0x00F0:  74 6D 6C 00 A0 0B 00 09 6C 6F 63 61 6C 68 6F 73    tml.....localhos\n0x0100:  74 00 0A 00 21 6A 61 76 61 78 2E 73 65 72 76 6C    t...!javax.servl\n0x0110:  65 74 2E 69 6E 63 6C 75 64 65 2E 72 65 71 75 65    et.include.reque\n0x0120:  73 74 5F 75 72 69 00 00 01 31 00 0A 00 1F 6A 61    st_uri...1....ja\n0x0130:  76 61 78 2E 73 65 72 76 6C 65 74 2E 69 6E 63 6C    vax.servlet.incl\n0x0140:  75 64 65 2E 70 61 74 68 5F 69 6E 66 6F 00 00 10    ude.path_info...\n0x0150:  2F 57 45 42 2D 49 4E 46 2F 77 65 62 2E 78 6D 6C    /WEB-INF/web.xml\n0x0160:  00 0A 00 22 6A 61 76 61 78 2E 73 65 72 76 6C 65    ..."javax.servle\n0x0170:  74 2E 69 6E 63 6C 75 64 65 2E 73 65 72 76 6C 65    t.include.servle\n0x0180:  74 5F 70 61 74 68 00 00 00 00 FF                   t_path.....']</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -10129,10 +9873,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H130" t="n">
+        <v>8080</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -10204,10 +9946,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H131" t="n">
+        <v>8080</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -10279,10 +10019,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H132" t="n">
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -10354,10 +10092,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H133" t="n">
+        <v>0</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -10429,10 +10165,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
+      <c r="H134" t="n">
+        <v>8009</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -10504,10 +10238,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H135" t="n">
+        <v>8080</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -10579,10 +10311,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H136" t="n">
+        <v>0</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -10654,10 +10384,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H137" t="n">
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -10729,10 +10457,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H138" t="n">
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -10804,10 +10530,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H139" t="n">
+        <v>8080</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -10879,10 +10603,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H140" t="n">
+        <v>8080</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -10954,10 +10676,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H141" t="n">
+        <v>0</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -11029,10 +10749,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H142" t="n">
+        <v>8080</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -11056,7 +10774,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>['Response Code : HTTP/1.1 200 OK', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : no\nOptions allowed : GET, HEAD, POST, PUT, DELETE, OPTIONS\nHeaders :', 'Server: Apache-Coyote/1.1\n  Accept-Ranges: bytes\n  ETag: W/"7454-1491118183000"\n  Last-Modified: Sun, 02 Apr 2017 07:29:43 GMT\n  Content-Type: text/html\n  Content-Length: 7454\n  Date: Thu, 23 Jul 2026 23:50:30 GMT', 'Response Body :', '&lt;!--\n  Licensed to the Apache Software Foundation (ASF) under one or more\n  contributor license agreements.  See the NOTICE file distributed with\n  this work for additional information regarding copyright ownership.\n  The ASF licenses this file to You under the Apache License, Version 2.0\n  (the "License"); you may not use this file except in compliance with\n  the License.  You may obtain a copy of the License at', 'http://www.apache.org/licenses/LICENSE-2.0', 'Unless required by applicable law or agreed to in writing, software\n  distributed under the License is distributed on an "AS IS" BASIS,\n  WITHOUT WARRANTIES OR CONDITIONS OF ANY KIND, either express or implied.\n  See the License for the specific language governing permissions and\n  limitations under the License.\n--&gt;\n&lt;?xml version="1.0" encoding="ISO-8859-1"?&gt;\n&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Strict//EN"\n   "http://www.w3.org/TR/xhtml1/DTD/xhtml1-strict.dtd"&gt;\n&lt;html xmlns="http://www.w3.org/1999/xhtml" xml:lang="en" lang="en"&gt;\n    &lt;head&gt;\n    &lt;title&gt;Apache Tomcat&lt;/title&gt;\n    &lt;style type="text/css"&gt;\n    /*&lt;![CDATA[*/\n      body {\n          color: #000000;\n          background-color: #FFFFFF;\n          font-family: Arial, "Times New Roman", Times, serif;\n          margin: 10px 0px;\n      }', 'img {\n       border: none;\n    }', 'a:link, a:visited {\n        color: blue\n    }', 'th {\n        font-family: Verdana, "Times New Roman", Times, serif;\n        font-size: 110%;\n        font-weight: normal;\n        font-style: italic;\n        background: #D2A41C;\n        text-align: left;\n    }', 'td {\n        color: #000000;\n        font-family: Arial, Helvetica, sans-serif;\n    }', 'td.menu {\n        background: #FFDC75;\n    }', '.center {\n        text-align: center;\n    }', '.code {\n        color: #000000;\n        font-family: "Courier New", Courier, monospace;\n        font-size: 110%;\n        margin-left: 2.5em;\n    }', '#banner {\n        margin-bottom: 12px;\n     }', 'p#congrats {\n         margin-top: 0;\n         font-weight: bold;\n         text-align: center;\n     }', 'p#footer {\n         text-align: right;\n         font-size: 80%;\n     }\n     /*]]&gt;*/\n   &lt;/style&gt;\n&lt;/head&gt;', '&lt;body&gt;', '&lt;!-- Header --&gt;\n&lt;table id="banner" width="100%"&gt;\n    &lt;tr&gt;\n      &lt;td align="left" style="width:130px"&gt;\n        &lt;a href="http://tomcat.apache.org/"&gt;\n          &lt;img src="tomcat.gif" height="92" width="130" alt="The Mighty Tomcat - MEOW!"/&gt;\n        &lt;/a&gt;\n      &lt;/td&gt;\n      &lt;td align="left" valign="top"&gt;&lt;b&gt;Apache Tomcat&lt;/b&gt;&lt;/td&gt;\n      &lt;td align="right"&gt;\n        &lt;a href="http://www.apache.org/"&gt;\n          &lt;img src="asf-logo-wide.svg" height="51" width="537" alt="The Apache Software Foundation"/&gt;\n        &lt;/a&gt;\n       &lt;/td&gt;\n     &lt;/tr&gt;\n&lt;/table&gt;', '&lt;table&gt;\n    &lt;tr&gt;', '&lt;!-- Table of Contents --&gt;\n        &lt;td valign="top"&gt;\n            &lt;table width="100%" border="1" cellspacing="0" cellpadding="3"&gt;\n                &lt;tr&gt;\n                  &lt;th&gt;Administration&lt;/th&gt;\n                &lt;/tr&gt;\n                &lt;tr&gt;\n                  &lt;td class="menu"&gt;\n                    &lt;a href="/manager/status"&gt;Status&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="/manager/html"&gt;Tomcat&amp;nbsp;Manager&lt;/a&gt;&lt;br/&gt;\n                    &amp;nbsp;\n                  &lt;/td&gt;\n                &lt;/tr&gt;\n            &lt;/table&gt;\n            &lt;br /&gt;\n            &lt;table width="100%" border="1" cellspacing="0" cellpadding="3"&gt;\n                &lt;tr&gt;\n                  &lt;th&gt;Documentation&lt;/th&gt;\n                &lt;/tr&gt;\n                &lt;tr&gt;\n                  &lt;td class="menu"&gt;\n                    &lt;a href="RELEASE-NOTES.txt"&gt;Release&amp;nbsp;Notes&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="/docs/changelog.html"&gt;Change&amp;nbsp;Log&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="/docs"&gt;Tomcat&amp;nbsp;Documentation&lt;/a&gt;&lt;br/&gt;\n                    &amp;nbsp;\n                    &lt;/td&gt;\n                &lt;/tr&gt;\n            &lt;/table&gt;\n            &lt;br/&gt;\n            &lt;table width="100%" border="1" cellspacing="0" cellpadding="3"&gt;\n                &lt;tr&gt;\n                  &lt;th&gt;Tomcat Online&lt;/th&gt;\n                &lt;/tr&gt;\n                &lt;tr&gt;\n                  &lt;td class="menu"&gt;\n                    &lt;a href="http://tomcat.apache.org/"&gt;Home&amp;nbsp;Page&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="http://tomcat.apache.org/faq/"&gt;FAQ&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="http://tomcat.apache.org/bugreport.html"&gt;Bug&amp;nbsp;Database&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="http://mail-archives.apache.org/mod_mbox/tomcat-users/"&gt;Users&amp;nbsp;Mailing&amp;nbsp;List&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="http://mail-archives.apache.org/mod_mbox/tomcat-dev/"&gt;Developers&amp;nbsp;Mailing&amp;nbsp;List&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="irc://irc.freenode.net/#tomcat"&gt;IRC&lt;/a&gt;&lt;br/&gt;\n                    &amp;nbsp;\n                  &lt;/td&gt;\n                &lt;/tr&gt;\n            &lt;/table&gt;\n            &lt;br/&gt;\n            &lt;table width="100%" border="1" cellspacing="0" cellpadding="3"&gt;\n                &lt;tr&gt;\n                  &lt;th&gt;Miscellaneous&lt;/th&gt;\n                &lt;/tr&gt;\n                &lt;tr&gt;\n                  &lt;td class="menu"&gt;\n                    &lt;a href="/examples/servlets/"&gt;Servlets Examples&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="/examples/jsp/"&gt;JSP Examples&lt;/a&gt;&lt;br/&gt;\n                    &lt;a href="http://wiki.apache.org/tomcat/Specifications"&gt;Specifications&lt;/a&gt;&lt;br/&gt;\n                        &amp;nbsp;\n                  &lt;/td&gt;\n                &lt;/tr&gt;\n            &lt;/table&gt;\n        &lt;/td&gt;', '&lt;td style="width:20px"&gt;&amp;nbsp;&lt;/td&gt;', '&lt;!-- Body --&gt;\n        &lt;td align="left" valign="top"&gt;\n          &lt;p id="congrats"&gt;If you\'re seeing this page via a web browser, it means you\'ve setup Tomcat successfully. Congratulations!&lt;/p&gt;', '&lt;p&gt;As you may have guessed by now, this is the default Tomcat home page. It can be found on the local filesystem at:&lt;/p&gt;\n          &lt;p class="code"&gt;$CATALINA_HOME/webapps/ROOT/index.html&lt;/p&gt;', '&lt;p&gt;where "$CATALINA_HOME" is the root of the Tomcat installation directory. If you\'re seeing this page, and you don\'t think you should be, then you\'re either a user who has arrived at new installation of Tomcat, or you\'re an administrator who hasn\'t got his/her setup quite right. Providing the latter is the case, please refer to the &lt;a href="/docs"&gt;Tomcat Documentation&lt;/a&gt; for more detailed setup and administration information than is found in the INSTALL file.&lt;/p&gt;', '&lt;p&gt;&lt;b&gt;NOTE: For security reasons, using the manager webapp\n            is restricted to users with certain roles such as "manager-gui".&lt;/b&gt;\n            Users are defined in &lt;code&gt;$CATALINA_HOME/conf/tomcat-users.xml&lt;/code&gt;.&lt;/p&gt;', '&lt;p&gt;Included with this release are a host of sample Servlets and JSPs (with associated source code), extensive documentation, and an introductory guide to developing web applications.&lt;/p&gt;', '&lt;p&gt;Tomcat mailing lists are available at the Tomcat project web site:&lt;/p&gt;', '&lt;ul&gt;\n               &lt;li&gt;&lt;b&gt;&lt;a href="http://tomcat.apache.org/lists.html#tomcat-users"&gt;tomcat-users&lt;/a&gt;&lt;/b&gt; for general questions related to configuring and using Tomcat&lt;/li&gt;\n               &lt;li&gt;&lt;b&gt;&lt;a href="http://tomcat.apache.org/lists.html#tomcat-dev"&gt;tomcat-dev&lt;/a&gt;&lt;/b&gt; for developers working on Tomcat&lt;/li&gt;\n           &lt;/ul&gt;', '&lt;p&gt;Thanks for using Tomcat!&lt;/p&gt;', '&lt;p id="footer"&gt;&lt;img src="tomcat-power.gif" width="77" height="80" alt="Powered by Tomcat"/&gt;&lt;br/&gt;\n            &amp;nbsp;', 'Copyright &amp;copy; 1999-2017 Apache Software Foundation&lt;br/&gt;\n            All Rights Reserved\n            &lt;/p&gt;\n        &lt;/td&gt;', '&lt;/tr&gt;\n&lt;/table&gt;', '&lt;/body&gt;\n&lt;/html&gt;']</t>
+          <t>['Response Code : HTTP/1.1 200 OK', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : no\nOptions allowed : GET, HEAD, POST, PUT, DELETE, OPTIONS\nHeaders :', 'Server: Apache-Coyote/1.1\n  Accept-Ranges: bytes\n  ETag: W/"7454-1491118183000"\n  Last-Modified: Sun, 02 Apr 2017 07:29:43 GMT\n  Content-Type: text/html\n  Content-Length: 7454\n  Date: Thu, 23 Jul 2026 23:50:30 GMT', 'Response Body :', '&lt;!--\n  Licensed to the Apache Software Foundation (ASF) under one or more\n  contributor license agreements.  See the NOTICE file distributed with\n  this work for additional information regarding copyright ownership.\n  The ASF licenses this file to You under the Apache License, Version 2.0\n  (the "License"); you may not use this file except in compliance with\n  the License.  You may obtain a copy of the License at', 'http://www.apache.org/licenses/LICENSE-2.0', 'Unless required by applicable law or agreed to in writing, software\n  distributed under the License is distributed on an "AS IS" BASIS,\n  WITHOUT WARRANTIES OR CONDITIONS OF ANY KIND, either express or implied.\n  See the License for the specific language governing permissions and\n  limitations under the License.\n--&gt;\n&lt;?xml version="1.0" encoding="ISO-8859-1"?&gt;\n&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Strict//EN"\n   "http://www.w3.org/TR/xhtml1/DTD/xhtml1-strict.dtd"&gt;\n&lt;html xmlns="http://www.w3.org/1999/xhtml" xml:lang="en" lang="en"&gt;\n    &lt;head&gt;\n    &lt;title&gt;Apache Tomcat&lt;/title&gt;\n    &lt;style type="text/css"&gt;\n    /*&lt;![CDATA[*/\n      body {\n          color: #000000;\n          background-color: #FFFFFF;\n          font-family: Arial, "Times New Roman", Times, serif;\n          margin: 10px 0px;\n      }', 'img {\n       border: none;\n    }', 'a:link, a:visited {\n        color: blue\n    }', 'th {\n        font-family: Verdana, "Times New Roman", Times, serif;\n        font-size: 110%;\n        font-weight: normal;\n        font-style: italic;\n        background: #D2A41C;\n        text-align: left;\n    }', '&lt;body&gt;', '&lt;/body&gt;\n&lt;/html&gt;']</t>
         </is>
       </c>
       <c r="N142" t="n">
@@ -11104,10 +10822,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
+      <c r="H143" t="n">
+        <v>8009</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -11179,10 +10895,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H144" t="n">
+        <v>8080</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -11254,10 +10968,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H145" t="n">
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -11329,10 +11041,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H146" t="n">
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -11404,10 +11114,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H147" t="n">
+        <v>0</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -11479,10 +11187,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H148" t="n">
+        <v>8080</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -11554,10 +11260,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H149" t="n">
+        <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -11629,10 +11333,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H150" t="n">
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -11704,10 +11406,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H151" t="n">
+        <v>8080</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -11779,10 +11479,8 @@
           <t>172.31.1.16</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H152" t="n">
+        <v>8080</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -11854,10 +11552,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H153" t="n">
+        <v>0</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -11929,10 +11625,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H154" t="n">
+        <v>0</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -12004,10 +11698,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H155" t="n">
+        <v>0</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -12079,10 +11771,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H156" t="n">
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -12154,10 +11844,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H157" t="n">
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -12229,10 +11917,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H158" t="n">
+        <v>0</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -12304,10 +11990,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H159" t="n">
+        <v>3306</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -12379,10 +12063,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H160" t="n">
+        <v>3306</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -12454,10 +12136,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H161" t="n">
+        <v>0</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -12529,10 +12209,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H162" t="n">
+        <v>0</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -12604,10 +12282,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H163" t="n">
+        <v>0</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -12679,10 +12355,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H164" t="n">
+        <v>3306</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -12754,10 +12428,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H165" t="n">
+        <v>0</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -12829,10 +12501,8 @@
           <t>172.31.1.25</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H166" t="n">
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -12904,10 +12574,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H167" t="n">
+        <v>0</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -12979,10 +12647,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H168" t="n">
+        <v>0</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -13054,10 +12720,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H169" t="n">
+        <v>0</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -13129,10 +12793,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H170" t="n">
+        <v>0</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -13204,10 +12866,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H171" t="n">
+        <v>0</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -13279,10 +12939,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H172" t="n">
+        <v>8080</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -13354,10 +13012,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="H173" t="n">
+        <v>50000</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -13429,10 +13085,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H174" t="n">
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -13504,10 +13158,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="H175" t="n">
+        <v>50000</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -13579,10 +13231,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H176" t="n">
+        <v>8080</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -13654,10 +13304,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="H177" t="n">
+        <v>50000</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -13729,10 +13377,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H178" t="n">
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -13804,10 +13450,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H179" t="n">
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -13879,10 +13523,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H180" t="n">
+        <v>0</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -13954,10 +13596,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H181" t="n">
+        <v>8080</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -14029,10 +13669,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="H182" t="n">
+        <v>50000</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -14104,10 +13742,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H183" t="n">
+        <v>0</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -14179,10 +13815,8 @@
           <t>172.31.1.48</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H184" t="n">
+        <v>0</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -14254,10 +13888,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H185" t="n">
+        <v>0</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -14329,10 +13961,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H186" t="n">
+        <v>8080</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -14404,10 +14034,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H187" t="n">
+        <v>9090</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -14479,10 +14107,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H188" t="n">
+        <v>8080</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -14554,10 +14180,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H189" t="n">
+        <v>9090</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -14629,10 +14253,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H190" t="n">
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -14704,10 +14326,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H191" t="n">
+        <v>0</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -14779,10 +14399,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H192" t="n">
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -14854,10 +14472,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H193" t="n">
+        <v>0</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -14929,10 +14545,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H194" t="n">
+        <v>8080</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15004,10 +14618,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H195" t="n">
+        <v>9090</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15079,10 +14691,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H196" t="n">
+        <v>9090</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -15154,10 +14764,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H197" t="n">
+        <v>0</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -15229,10 +14837,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H198" t="n">
+        <v>8080</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -15304,10 +14910,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H199" t="n">
+        <v>9090</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -15379,10 +14983,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H200" t="n">
+        <v>8080</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -15454,10 +15056,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H201" t="n">
+        <v>9090</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -15529,10 +15129,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H202" t="n">
+        <v>0</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -15604,10 +15202,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H203" t="n">
+        <v>0</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -15679,10 +15275,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H204" t="n">
+        <v>0</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -15754,10 +15348,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H205" t="n">
+        <v>8080</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -15829,10 +15421,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H206" t="n">
+        <v>9090</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -15904,10 +15494,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H207" t="n">
+        <v>8080</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -15979,10 +15567,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H208" t="n">
+        <v>9090</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -16054,10 +15640,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H209" t="n">
+        <v>8080</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -16081,7 +15665,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>['Subject Name:', 'Common Name: localhost', 'Issuer Name:', 'Common Name: localhost', 'Serial Number: 59 A1 02 96 F7 75 2F DE 6B CE 14 35 F9 7C 83 03 A3 96 4B 25', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jun 03 07:28:55 2026 GMT\nNot Valid After: May 31 07:28:55 2036 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 BA A6 1A 0A A7 A2 8F 3A 4A 82 1A CB AF F0 E5 AC C4 D4 BF \n            68 CD 02 8F 4F C1 C8 4C C6 4B D4 85 6F 1B 18 1B CC 51 B2 BA \n            0B 8C 88 83 2E 5B 4F B5 60 CE 9F C9 C7 8A 73 57 0B B0 12 F4 \n            02 2A 41 A7 41 77 07 F0 CB D7 33 5F E3 70 61 35 77 4B 2D 9A \n            D1 D3 CC E2 70 18 53 41 61 0A 66 AB A3 22 53 95 E2 07 1A C3 \n            6A A5 DC FE 16 BB AF C7 2C F2 A8 00 1E 7C 98 1C D1 22 24 24 \n            4C B4 29 2D 1F 8D FD 9E 60 06 37 99 83 4E 56 DB 5F 2B 9E 57 \n            44 82 50 4C 7E AD FE 63 FB FC 9E 8A AD 5E C4 43 A7 62 21 51 \n            97 AF FD B4 91 AF 40 77 81 EB D1 63 1B 0A 31 91 64 E2 E3 5E \n            3E 60 44 E4 52 41 F6 89 42 38 A6 D6 91 E5 62 09 DE 86 CF 31 \n            36 77 88 4C DF A6 BA 1D C7 A5 24 A4 6F 97 E9 38 73 D8 3A F2 \n            D2 E0 90 11 00 A1 21 B8 F6 A9 D0 89 27 28 0D D0 A5 85 65 7D \n            48 44 B9 B8 E5 A4 6C 19 50 52 DA EF 2D DA A5 BC C5 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 A8 6E 09 C5 33 96 E9 F9 C4 C7 30 81 8E 59 B9 BC 11 3D D1 \n           5E 78 CB 28 3E D6 0A D8 F1 18 85 38 E4 C8 9F E9 29 4C 7B B2 \n           D1 BE AE 37 83 C4 F3 DA 40 27 C3 6A 25 A8 8C 1C 60 50 48 56 \n           47 D8 10 92 6F 16 6A 14 AA 63 9D 97 25 E3 E0 68 AF 6E 94 2C \n           74 B9 27 73 AA 04 25 02 8C 79 3F 42 80 79 A2 75 F2 5C 6B DC \n           34 DD 42 38 21 6C 31 54 2A 73 CE 36 9F 28 83 10 2F 8D 0F 75 \n           A5 E5 34 4E 78 33 5A A2 48 62 7A A7 D9 4E B7 21 F0 86 8E C7 \n           92 B6 7B 59 64 44 14 CC D9 F1 0B 3C 95 BF 37 41 A7 C8 4E A0 \n           48 5A C4 14 67 27 61 54 1B BA E2 D4 C8 E8 CF 0B 3F B6 EA 1B \n           07 ED 73 3F 97 B4 75 3F C1 72 D2 30 03 CD 66 13 9F FB 4C C5 \n           4A EE 78 86 C4 8D 9C 81 16 3C D3 28 82 93 D7 53 A5 C0 2E 55 \n           08 4C BC 8C 87 4E 20 0F 89 B1 E4 83 88 3E FE E5 CA 4B C7 B8 \n           C2 63 F4 C5 92 83 7E 81 10 52 22 41 AC A2 E7 80 8D', 'Extension: Basic Constraints(2.5.29.19)\nCritical: 0', 'Extension: Subject Alternative Name(2.5.29.17)\nCritical: 0\nDNS: localhost', 'Extension: Subject Key Identifier(2.5.29.14)\nCritical: 0\nSubject Key Identifier: 89 F5 79 1C 5D 3B 74 8C 7F 3B 46 E4 3E 55 A6 35 31 1C 87 BF', 'Fingerprints :', 'SHA-256 Fingerprint: DB EE 75 ED 39 33 8F C8 45 FB A9 C6 7B D0 BB E6 66 90 2D C5 \n                     06 F5 97 9C 62 DB 80 31 28 25 47 40 \nSHA-1 Fingerprint: 79 D6 19 C0 5C 63 A6 4F F2 7E 1D 31 2C 01 E2 4A 3D 93 F4 54 \nMD5 Fingerprint: EB 21 7B DE BD E9 BD AF F2 9C DC D4 BB 35 7F 52', 'PEM certificate :', '-----BEGIN CERTIFICATE-----\nMIIC+DCCAeCgAwIBAgIUWaEClvd1L95rzhQ1+XyDA6OWSyUwDQYJKoZIhvcNAQELBQAwFDESMBAGA1UEAwwJbG9jYWxob3N0MB4XDTI2MDYwMzA3Mjg1NVoXDTM2MDUzMTA3Mjg1NVowFDESMBAGA1UEAwwJbG9jYWxob3N0MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAuqYaCqeijzpKghrLr/DlrMTUv2jNAo9PwchMxkvUhW8bGBvMUbK6C4yIgy5bT7Vgzp/Jx4pzVwuwEvQCKkGnQXcH8MvXM1/jcGE1d0stmtHTzOJwGFNBYQpmq6MiU5XiBxrDaqXc/ha7r8cs8qgAHnyYHNEiJCRMtCktH439nmAGN5mDTlbbXyueV0SCUEx+rf5j+/yeiq1exEOnYiFRl6/9tJGvQHeB69FjGwoxkWTi414+YETkUkH2iUI4ptaR5WIJ3obPMTZ3iEzfprodx6UkpG+X6Thz2Dry0uCQEQChIbj2qdCJJygN0KWFZX1IRLm45aRsGVBS2u8t2qW8xQIDAQABo0IwQDAJBgNVHRMEAjAAMBQGA1UdEQQNMAuCCWxvY2FsaG9zdDAdBgNVHQ4EFgQUifV5HF07dIx/O0bkPlWmNTEch78wDQYJKoZIhvcNAQELBQADggEBAKhuCcUzlun5xMcwgY5ZubwRPdFeeMsoPtYK2PEYhTjkyJ/pKUx7stG+rjeDxPPaQCfDaiWojBxgUEhWR9gQkm8WahSqY52XJePgaK9ulCx0uSdzqgQlAox5P0KAeaJ18lxr3DTdQjghbDFUKnPONp8ogxAvjQ91peU0TngzWqJIYnqn2U63IfCGjseStntZZEQUzNnxCzyVvzdBp8hOoEhaxBRnJ2FUG7ri1Mjozws/tuobB+1zP5e0dT/BctIwA81mE5/7TMVK7niGxI2cgRY80yiCk9dTpcAuVQhMvIyHTiAPibHkg4g+/uXKS8e4wmP0xZKDfoEQUiJBrKLngI0=\n-----END CERTIFICATE-----']</t>
+          <t>['Subject Name:', 'Common Name: localhost', 'Issuer Name:', 'Common Name: localhost', 'Serial Number: 59 A1 02 96 F7 75 2F DE 6B CE 14 35 F9 7C 83 03 A3 96 4B 25', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jun 03 07:28:55 2026 GMT\nNot Valid After: May 31 07:28:55 2036 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 BA A6 1A 0A A7 A2 8F 3A 4A 82 1A CB AF F0 E5 AC C4 D4 BF \n            68 CD 02 8F 4F C1 C8 4C C6 4B D4 85 6F 1B 18 1B CC 51 B2 BA \n            0B 8C 88 83 2E 5B 4F B5 60 CE 9F C9 C7 8A 73 57 0B B0 12 F4 \n            02 2A 41 A7 41 77 07 F0 CB D7 33 5F E3 70 61 35 77 4B 2D 9A \n            D1 D3 CC E2 70 18 53 41 61 0A 66 AB A3 22 53 95 E2 07 1A C3 \n            6A A5 DC FE 16 BB AF C7 2C F2 A8 00 1E 7C 98 1C D1 22 24 24 \n            4C B4 29 2D 1F 8D FD 9E 60 06 37 99 83 4E 56 DB 5F 2B 9E 57 \n            44 82 50 4C 7E AD FE 63 FB FC 9E 8A AD 5E C4 43 A7 62 21 51 \n            97 AF FD B4 91 AF 40 77 81 EB D1 63 1B 0A 31 91 64 E2 E3 5E \n            3E 60 44 E4 52 41 F6 89 42 38 A6 D6 91 E5 62 09 DE 86 CF 31 \n            36 77 88 4C DF A6 BA 1D C7 A5 24 A4 6F 97 E9 38 73 D8 3A F2 \n            D2 E0 90 11 00 A1 21 B8 F6 A9 D0 89 27 28 0D D0 A5 85 65 7D \n            48 44 B9 B8 E5 A4 6C 19 50 52 DA EF 2D DA A5 BC C5 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 A8 6E 09 C5 33 96 E9 F9 C4 C7 30 81 8E 59 B9 BC 11 3D D1 \n           5E 78 CB 28 3E D6 0A D8 F1 18 85 38 E4 C8 9F E9 29 4C 7B B2 \n           D1 BE AE 37 83 C4 F3 DA 40 27 C3 6A 25 A8 8C 1C 60 50 48 56 \n           47 D8 10 92 6F 16 6A 14 AA 63 9D 97 25 E3 E0 68 AF 6E 94 2C \n           74 B9 27 73 AA 04 25 02 8C 79 3F 42 80 79 A2 75 F2 5C 6B DC \n           34 DD 42 38 21 6C 31 54 2A 73 CE 36 9F 28 83 10 2F 8D 0F 75 \n           A5 E5 34 4E 78 33 5A A2 48 62 7A A7 D9 4E B7 21 F0 86 8E C7 \n           92 B6 7B 59 64 44 14 CC D9 F1 0B 3C 95 BF 37 41 A7 C8 4E A0 \n           48 5A C4 14 67 27 61 54 1B BA E2 D4 C8 E8 CF 0B 3F B6 EA 1B \n           07 ED 73 3F 97 B4 75 3F C1 72 D2 30 03 CD 66 13 9F FB 4C C5 \n           4A EE 78 86 C4 8D 9C 81 16 3C D3 28 82 93 D7 53 A5 C0 2E 55 \n           08 4C BC 8C 87 4E 20 0F 89 B1 E4 83 88 3E FE E5 CA 4B C7 B8 \n           C2 63 F4 C5 92 83 7E 81 10 52 22 41 AC A2 E7 80 8D']</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -16129,10 +15713,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H210" t="n">
+        <v>9090</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -16156,7 +15738,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>['Subject Name:', 'Common Name: localhost', 'Issuer Name:', 'Common Name: localhost', 'Serial Number: 59 A1 02 96 F7 75 2F DE 6B CE 14 35 F9 7C 83 03 A3 96 4B 25', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jun 03 07:28:55 2026 GMT\nNot Valid After: May 31 07:28:55 2036 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 BA A6 1A 0A A7 A2 8F 3A 4A 82 1A CB AF F0 E5 AC C4 D4 BF \n            68 CD 02 8F 4F C1 C8 4C C6 4B D4 85 6F 1B 18 1B CC 51 B2 BA \n            0B 8C 88 83 2E 5B 4F B5 60 CE 9F C9 C7 8A 73 57 0B B0 12 F4 \n            02 2A 41 A7 41 77 07 F0 CB D7 33 5F E3 70 61 35 77 4B 2D 9A \n            D1 D3 CC E2 70 18 53 41 61 0A 66 AB A3 22 53 95 E2 07 1A C3 \n            6A A5 DC FE 16 BB AF C7 2C F2 A8 00 1E 7C 98 1C D1 22 24 24 \n            4C B4 29 2D 1F 8D FD 9E 60 06 37 99 83 4E 56 DB 5F 2B 9E 57 \n            44 82 50 4C 7E AD FE 63 FB FC 9E 8A AD 5E C4 43 A7 62 21 51 \n            97 AF FD B4 91 AF 40 77 81 EB D1 63 1B 0A 31 91 64 E2 E3 5E \n            3E 60 44 E4 52 41 F6 89 42 38 A6 D6 91 E5 62 09 DE 86 CF 31 \n            36 77 88 4C DF A6 BA 1D C7 A5 24 A4 6F 97 E9 38 73 D8 3A F2 \n            D2 E0 90 11 00 A1 21 B8 F6 A9 D0 89 27 28 0D D0 A5 85 65 7D \n            48 44 B9 B8 E5 A4 6C 19 50 52 DA EF 2D DA A5 BC C5 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 A8 6E 09 C5 33 96 E9 F9 C4 C7 30 81 8E 59 B9 BC 11 3D D1 \n           5E 78 CB 28 3E D6 0A D8 F1 18 85 38 E4 C8 9F E9 29 4C 7B B2 \n           D1 BE AE 37 83 C4 F3 DA 40 27 C3 6A 25 A8 8C 1C 60 50 48 56 \n           47 D8 10 92 6F 16 6A 14 AA 63 9D 97 25 E3 E0 68 AF 6E 94 2C \n           74 B9 27 73 AA 04 25 02 8C 79 3F 42 80 79 A2 75 F2 5C 6B DC \n           34 DD 42 38 21 6C 31 54 2A 73 CE 36 9F 28 83 10 2F 8D 0F 75 \n           A5 E5 34 4E 78 33 5A A2 48 62 7A A7 D9 4E B7 21 F0 86 8E C7 \n           92 B6 7B 59 64 44 14 CC D9 F1 0B 3C 95 BF 37 41 A7 C8 4E A0 \n           48 5A C4 14 67 27 61 54 1B BA E2 D4 C8 E8 CF 0B 3F B6 EA 1B \n           07 ED 73 3F 97 B4 75 3F C1 72 D2 30 03 CD 66 13 9F FB 4C C5 \n           4A EE 78 86 C4 8D 9C 81 16 3C D3 28 82 93 D7 53 A5 C0 2E 55 \n           08 4C BC 8C 87 4E 20 0F 89 B1 E4 83 88 3E FE E5 CA 4B C7 B8 \n           C2 63 F4 C5 92 83 7E 81 10 52 22 41 AC A2 E7 80 8D', 'Extension: Basic Constraints(2.5.29.19)\nCritical: 0', 'Extension: Subject Alternative Name(2.5.29.17)\nCritical: 0\nDNS: localhost', 'Extension: Subject Key Identifier(2.5.29.14)\nCritical: 0\nSubject Key Identifier: 89 F5 79 1C 5D 3B 74 8C 7F 3B 46 E4 3E 55 A6 35 31 1C 87 BF', 'Fingerprints :', 'SHA-256 Fingerprint: DB EE 75 ED 39 33 8F C8 45 FB A9 C6 7B D0 BB E6 66 90 2D C5 \n                     06 F5 97 9C 62 DB 80 31 28 25 47 40 \nSHA-1 Fingerprint: 79 D6 19 C0 5C 63 A6 4F F2 7E 1D 31 2C 01 E2 4A 3D 93 F4 54 \nMD5 Fingerprint: EB 21 7B DE BD E9 BD AF F2 9C DC D4 BB 35 7F 52', 'PEM certificate :', '-----BEGIN CERTIFICATE-----\nMIIC+DCCAeCgAwIBAgIUWaEClvd1L95rzhQ1+XyDA6OWSyUwDQYJKoZIhvcNAQELBQAwFDESMBAGA1UEAwwJbG9jYWxob3N0MB4XDTI2MDYwMzA3Mjg1NVoXDTM2MDUzMTA3Mjg1NVowFDESMBAGA1UEAwwJbG9jYWxob3N0MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAuqYaCqeijzpKghrLr/DlrMTUv2jNAo9PwchMxkvUhW8bGBvMUbK6C4yIgy5bT7Vgzp/Jx4pzVwuwEvQCKkGnQXcH8MvXM1/jcGE1d0stmtHTzOJwGFNBYQpmq6MiU5XiBxrDaqXc/ha7r8cs8qgAHnyYHNEiJCRMtCktH439nmAGN5mDTlbbXyueV0SCUEx+rf5j+/yeiq1exEOnYiFRl6/9tJGvQHeB69FjGwoxkWTi414+YETkUkH2iUI4ptaR5WIJ3obPMTZ3iEzfprodx6UkpG+X6Thz2Dry0uCQEQChIbj2qdCJJygN0KWFZX1IRLm45aRsGVBS2u8t2qW8xQIDAQABo0IwQDAJBgNVHRMEAjAAMBQGA1UdEQQNMAuCCWxvY2FsaG9zdDAdBgNVHQ4EFgQUifV5HF07dIx/O0bkPlWmNTEch78wDQYJKoZIhvcNAQELBQADggEBAKhuCcUzlun5xMcwgY5ZubwRPdFeeMsoPtYK2PEYhTjkyJ/pKUx7stG+rjeDxPPaQCfDaiWojBxgUEhWR9gQkm8WahSqY52XJePgaK9ulCx0uSdzqgQlAox5P0KAeaJ18lxr3DTdQjghbDFUKnPONp8ogxAvjQ91peU0TngzWqJIYnqn2U63IfCGjseStntZZEQUzNnxCzyVvzdBp8hOoEhaxBRnJ2FUG7ri1Mjozws/tuobB+1zP5e0dT/BctIwA81mE5/7TMVK7niGxI2cgRY80yiCk9dTpcAuVQhMvIyHTiAPibHkg4g+/uXKS8e4wmP0xZKDfoEQUiJBrKLngI0=\n-----END CERTIFICATE-----']</t>
+          <t>['Subject Name:', 'Common Name: localhost', 'Issuer Name:', 'Common Name: localhost', 'Serial Number: 59 A1 02 96 F7 75 2F DE 6B CE 14 35 F9 7C 83 03 A3 96 4B 25', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jun 03 07:28:55 2026 GMT\nNot Valid After: May 31 07:28:55 2036 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 BA A6 1A 0A A7 A2 8F 3A 4A 82 1A CB AF F0 E5 AC C4 D4 BF \n            68 CD 02 8F 4F C1 C8 4C C6 4B D4 85 6F 1B 18 1B CC 51 B2 BA \n            0B 8C 88 83 2E 5B 4F B5 60 CE 9F C9 C7 8A 73 57 0B B0 12 F4 \n            02 2A 41 A7 41 77 07 F0 CB D7 33 5F E3 70 61 35 77 4B 2D 9A \n            D1 D3 CC E2 70 18 53 41 61 0A 66 AB A3 22 53 95 E2 07 1A C3 \n            6A A5 DC FE 16 BB AF C7 2C F2 A8 00 1E 7C 98 1C D1 22 24 24 \n            4C B4 29 2D 1F 8D FD 9E 60 06 37 99 83 4E 56 DB 5F 2B 9E 57 \n            44 82 50 4C 7E AD FE 63 FB FC 9E 8A AD 5E C4 43 A7 62 21 51 \n            97 AF FD B4 91 AF 40 77 81 EB D1 63 1B 0A 31 91 64 E2 E3 5E \n            3E 60 44 E4 52 41 F6 89 42 38 A6 D6 91 E5 62 09 DE 86 CF 31 \n            36 77 88 4C DF A6 BA 1D C7 A5 24 A4 6F 97 E9 38 73 D8 3A F2 \n            D2 E0 90 11 00 A1 21 B8 F6 A9 D0 89 27 28 0D D0 A5 85 65 7D \n            48 44 B9 B8 E5 A4 6C 19 50 52 DA EF 2D DA A5 BC C5 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 A8 6E 09 C5 33 96 E9 F9 C4 C7 30 81 8E 59 B9 BC 11 3D D1 \n           5E 78 CB 28 3E D6 0A D8 F1 18 85 38 E4 C8 9F E9 29 4C 7B B2 \n           D1 BE AE 37 83 C4 F3 DA 40 27 C3 6A 25 A8 8C 1C 60 50 48 56 \n           47 D8 10 92 6F 16 6A 14 AA 63 9D 97 25 E3 E0 68 AF 6E 94 2C \n           74 B9 27 73 AA 04 25 02 8C 79 3F 42 80 79 A2 75 F2 5C 6B DC \n           34 DD 42 38 21 6C 31 54 2A 73 CE 36 9F 28 83 10 2F 8D 0F 75 \n           A5 E5 34 4E 78 33 5A A2 48 62 7A A7 D9 4E B7 21 F0 86 8E C7 \n           92 B6 7B 59 64 44 14 CC D9 F1 0B 3C 95 BF 37 41 A7 C8 4E A0 \n           48 5A C4 14 67 27 61 54 1B BA E2 D4 C8 E8 CF 0B 3F B6 EA 1B \n           07 ED 73 3F 97 B4 75 3F C1 72 D2 30 03 CD 66 13 9F FB 4C C5 \n           4A EE 78 86 C4 8D 9C 81 16 3C D3 28 82 93 D7 53 A5 C0 2E 55 \n           08 4C BC 8C 87 4E 20 0F 89 B1 E4 83 88 3E FE E5 CA 4B C7 B8 \n           C2 63 F4 C5 92 83 7E 81 10 52 22 41 AC A2 E7 80 8D']</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -16204,10 +15786,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H211" t="n">
+        <v>8080</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -16279,10 +15859,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H212" t="n">
+        <v>9090</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -16354,10 +15932,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H213" t="n">
+        <v>8080</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -16429,10 +16005,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H214" t="n">
+        <v>9090</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -16504,10 +16078,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H215" t="n">
+        <v>8080</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -16579,10 +16151,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H216" t="n">
+        <v>9090</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -16654,10 +16224,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H217" t="n">
+        <v>8080</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -16729,10 +16297,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H218" t="n">
+        <v>9090</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -16804,10 +16370,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H219" t="n">
+        <v>8080</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -16879,10 +16443,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H220" t="n">
+        <v>9090</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -16954,10 +16516,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H221" t="n">
+        <v>0</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17029,10 +16589,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H222" t="n">
+        <v>0</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17104,10 +16662,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H223" t="n">
+        <v>9090</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17179,10 +16735,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H224" t="n">
+        <v>8080</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17254,10 +16808,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H225" t="n">
+        <v>9090</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -17329,10 +16881,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H226" t="n">
+        <v>8080</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -17404,10 +16954,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H227" t="n">
+        <v>9090</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -17479,10 +17027,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
+      <c r="H228" t="n">
+        <v>8080</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -17554,10 +17100,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
+      <c r="H229" t="n">
+        <v>9090</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -17629,10 +17173,8 @@
           <t>172.31.1.100</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H230" t="n">
+        <v>0</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -17704,10 +17246,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H231" t="n">
+        <v>53</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -17779,10 +17319,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H232" t="n">
+        <v>0</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -17854,10 +17392,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H233" t="n">
+        <v>10000</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -17929,10 +17465,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H234" t="n">
+        <v>10000</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -18004,10 +17538,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H235" t="n">
+        <v>10000</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -18079,10 +17611,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H236" t="n">
+        <v>0</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -18154,10 +17684,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H237" t="n">
+        <v>0</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -18229,10 +17757,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H238" t="n">
+        <v>0</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18304,10 +17830,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H239" t="n">
+        <v>53</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -18379,10 +17903,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H240" t="n">
+        <v>53</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -18454,10 +17976,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H241" t="n">
+        <v>53</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -18529,10 +18049,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H242" t="n">
+        <v>53</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -18604,10 +18122,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H243" t="n">
+        <v>53</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -18679,10 +18195,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H244" t="n">
+        <v>0</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -18754,10 +18268,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H245" t="n">
+        <v>10000</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -18829,10 +18341,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H246" t="n">
+        <v>0</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -18904,10 +18414,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H247" t="n">
+        <v>10000</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -18979,10 +18487,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H248" t="n">
+        <v>0</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19054,10 +18560,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H249" t="n">
+        <v>53</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19129,10 +18633,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H250" t="n">
+        <v>10000</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19204,10 +18706,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H251" t="n">
+        <v>0</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19279,10 +18779,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H252" t="n">
+        <v>0</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19354,10 +18852,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H253" t="n">
+        <v>0</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -19429,10 +18925,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H254" t="n">
+        <v>10000</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -19504,10 +18998,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H255" t="n">
+        <v>10000</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -19579,10 +19071,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H256" t="n">
+        <v>10000</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -19606,7 +19096,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>['Subject Name:', 'Organization: Webmin Webserver on 3ba0a6fbea8e\nCommon Name: *\nEmail Address: root@3ba0a6fbea8e', 'Issuer Name:', 'Organization: Webmin Webserver on 3ba0a6fbea8e\nCommon Name: *\nEmail Address: root@3ba0a6fbea8e', 'Serial Number: 67 26 3F 8B 6E AA 1E A9 C1 38 99 C0 F9 0A 80 15 A7 C2 C7 C0', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jul 06 04:22:57 2019 GMT\nNot Valid After: Jul 04 04:22:57 2024 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 E1 3E 47 1F 9C C9 D1 67 D9 68 08 AA 62 B7 D2 9A FC BB 8D \n            F7 3F A1 11 F8 CE CC 0F 59 E1 58 C7 1F A5 B2 FE 08 F3 25 82 \n            7B 7C 90 19 B6 E8 67 52 90 AC F8 1D 5F 10 94 E5 8D 45 E4 45 \n            C9 B2 F2 A4 3E 07 A7 91 A1 AE B2 F4 3D 96 1A 9F 77 86 2A 23 \n            CF 60 5E CE 08 25 F3 C1 9C 7A 40 CC 5A E7 9E 1C 69 CD 1E 93 \n            09 1B F6 A0 20 AB A9 2F 80 D3 45 E7 D4 37 58 EA 39 D0 75 12 \n            AF 50 C3 B4 50 7A D0 51 64 CF 77 9A 7D 01 BC DC EA F8 6D B7 \n            DF 3B 0F D8 AA 9D D6 F6 35 E6 33 85 E2 A6 7F 2D EF 0C 7F 65 \n            49 F1 9C 87 C6 68 2F 98 52 B3 F7 CA 90 DB 45 F4 52 4A 42 A5 \n            9F 31 EA 68 4C AA 48 5A 99 36 F7 B5 E2 1F 19 15 08 40 19 C5 \n            9B 13 BF D6 94 D5 6B E3 AF 43 B9 DB 34 18 37 6F 6C BB 06 0F \n            28 6F CD FA 0F 21 1A 58 84 5D 48 80 41 72 7F 33 93 69 C3 45 \n            9D F3 D2 A7 26 52 8E D6 D8 FB 54 65 92 11 02 28 F9 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 01 02 39 91 21 36 53 5A 8A 26 00 E3 EF 35 4B B0 E3 8F 0A \n           61 86 5B 4D 31 AA 27 ED 62 32 03 92 0F 8B 32 75 97 05 86 A6 \n           F4 46 0A F7 57 15 C3 7E 90 AA 22 3D 44 7C 73 CF 24 A9 38 1A \n           EA 99 EC ED 64 2E 15 BB C1 23 36 BE 8A C7 08 F9 DD 92 79 C1 \n           A5 DD 78 8D 23 12 07 00 CC FD 1B 5C F6 4F 32 F7 BF 45 47 F0 \n           54 76 7D 5F E9 08 7D 79 1F 2C D7 F1 97 38 20 4A F1 DD 67 07 \n           02 CC 21 0C 35 5F CB F2 2D 8A 8B ED 27 BA C6 2C 61 55 1D 8B \n           4C EC 37 61 48 98 4C AE 85 D9 9F 40 5B 1E 40 3F BF 73 39 15 \n           C5 14 F5 54 F6 6C 09 5D C7 0A 5F 7F AD 2F 4F 1E 0F 2A 72 2E \n           57 0D 0A 1B 82 C3 FD 5C D1 5B E0 56 F7 A3 69 A9 3D 68 3A 25 \n           20 EA B3 65 1F 4B EB DF BF 3B E0 AE 3C 1C 63 A6 06 F6 FA 65 \n           BB 32 9F 38 1B 0D E7 93 0F E8 2C 25 84 64 B3 98 5E 88 75 A4 \n           35 4D E0 8C D4 98 1D D8 F3 EB 49 A5 24 B5 02 04 12', 'Extension: Subject Key Identifier(2.5.29.14)\nCritical: 0\nSubject Key Identifier: 9D 97 79 9D D1 BE B8 83 B2 95 B6 0D 19 0C 61 1B 35 CB DB F2', 'Extension: Authority Key Identifier(2.5.29.35)\nCritical: 0\nKey Identifier: 9D 97 79 9D D1 BE B8 83 B2 95 B6 0D 19 0C 61 1B 35 CB DB F2', 'Extension: Basic Constraints(2.5.29.19)\nCritical: 1\nCA: TRUE', 'Fingerprints :', 'SHA-256 Fingerprint: 2D 92 9D F1 02 BC 72 C7 9E 82 88 25 6E 22 E8 B8 7B 6D 99 B2 \n                     E2 93 16 86 58 94 A1 63 AF B6 DF F1 \nSHA-1 Fingerprint: AC FF 91 A8 C8 4F A5 44 10 31 1C 1D 82 8A D2 0C 55 F9 B7 8F \nMD5 Fingerprint: 2E 42 72 80 1F BF C2 F4 1D C7 7A D3 9F CF 7D 7C', 'PEM certificate :', '-----BEGIN CERTIFICATE-----\nMIIDkzCCAnugAwIBAgIUZyY/i26qHqnBOJnA+QqAFafCx8AwDQYJKoZIhvcNAQELBQAwWTEpMCcGA1UECgwgV2VibWluIFdlYnNlcnZlciBvbiAzYmEwYTZmYmVhOGUxCjAIBgNVBAMMASoxIDAeBgkqhkiG9w0BCQEWEXJvb3RAM2JhMGE2ZmJlYThlMB4XDTE5MDcwNjA0MjI1N1oXDTI0MDcwNDA0MjI1N1owWTEpMCcGA1UECgwgV2VibWluIFdlYnNlcnZlciBvbiAzYmEwYTZmYmVhOGUxCjAIBgNVBAMMASoxIDAeBgkqhkiG9w0BCQEWEXJvb3RAM2JhMGE2ZmJlYThlMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA4T5HH5zJ0WfZaAiqYrfSmvy7jfc/oRH4zswPWeFYxx+lsv4I8yWCe3yQGbboZ1KQrPgdXxCU5Y1F5EXJsvKkPgenkaGusvQ9lhqfd4YqI89gXs4IJfPBnHpAzFrnnhxpzR6TCRv2oCCrqS+A00Xn1DdY6jnQdRKvUMO0UHrQUWTPd5p9Abzc6vhtt987D9iqndb2NeYzheKmfy3vDH9lSfGch8ZoL5hSs/fKkNtF9FJKQqWfMepoTKpIWpk297XiHxkVCEAZxZsTv9aU1Wvjr0O52zQYN29suwYPKG/N+g8hGliEXUiAQXJ/M5Npw0Wd89KnJlKO1tj7VGWSEQIo+QIDAQABo1MwUTAdBgNVHQ4EFgQUnZd5ndG+uIOylbYNGQxhGzXL2/IwHwYDVR0jBBgwFoAUnZd5ndG+uIOylbYNGQxhGzXL2/IwDwYDVR0TAQH/BAUwAwEB/zANBgkqhkiG9w0BAQsFAAOCAQEAAQI5kSE2U1qKJgDj7zVLsOOPCmGGW00xqiftYjIDkg+LMnWXBYam9EYK91cVw36QqiI9RHxzzySpOBrqmeztZC4Vu8EjNr6Kxwj53ZJ5waXdeI0jEgcAzP0bXPZPMve/RUfwVHZ9X+kIfXkfLNfxlzggSvHdZwcCzCEMNV/L8i2Ki+0nusYsYVUdi0zsN2FImEyuhdmfQFseQD+/czkVxRT1VPZsCV3HCl9/rS9PHg8qci5XDQobgsP9XNFb4Fb3o2mpPWg6JSDqs2UfS+vfvzvgrjwcY6YG9vpluzKfOBsN55MP6CwlhGSzmF6IdaQ1TeCM1Jgd2PPrSaUktQIEEg==\n-----END CERTIFICATE-----']</t>
+          <t>['Subject Name:', 'Organization: Webmin Webserver on 3ba0a6fbea8e\nCommon Name: *\nEmail Address: root@3ba0a6fbea8e', 'Issuer Name:', 'Organization: Webmin Webserver on 3ba0a6fbea8e\nCommon Name: *\nEmail Address: root@3ba0a6fbea8e', 'Serial Number: 67 26 3F 8B 6E AA 1E A9 C1 38 99 C0 F9 0A 80 15 A7 C2 C7 C0', 'Version: 3', 'Signature Algorithm: SHA-256 With RSA Encryption', 'Not Valid Before: Jul 06 04:22:57 2019 GMT\nNot Valid After: Jul 04 04:22:57 2024 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 2048 bits\nPublic Key: 00 E1 3E 47 1F 9C C9 D1 67 D9 68 08 AA 62 B7 D2 9A FC BB 8D \n            F7 3F A1 11 F8 CE CC 0F 59 E1 58 C7 1F A5 B2 FE 08 F3 25 82 \n            7B 7C 90 19 B6 E8 67 52 90 AC F8 1D 5F 10 94 E5 8D 45 E4 45 \n            C9 B2 F2 A4 3E 07 A7 91 A1 AE B2 F4 3D 96 1A 9F 77 86 2A 23 \n            CF 60 5E CE 08 25 F3 C1 9C 7A 40 CC 5A E7 9E 1C 69 CD 1E 93 \n            09 1B F6 A0 20 AB A9 2F 80 D3 45 E7 D4 37 58 EA 39 D0 75 12 \n            AF 50 C3 B4 50 7A D0 51 64 CF 77 9A 7D 01 BC DC EA F8 6D B7 \n            DF 3B 0F D8 AA 9D D6 F6 35 E6 33 85 E2 A6 7F 2D EF 0C 7F 65 \n            49 F1 9C 87 C6 68 2F 98 52 B3 F7 CA 90 DB 45 F4 52 4A 42 A5 \n            9F 31 EA 68 4C AA 48 5A 99 36 F7 B5 E2 1F 19 15 08 40 19 C5 \n            9B 13 BF D6 94 D5 6B E3 AF 43 B9 DB 34 18 37 6F 6C BB 06 0F \n            28 6F CD FA 0F 21 1A 58 84 5D 48 80 41 72 7F 33 93 69 C3 45 \n            9D F3 D2 A7 26 52 8E D6 D8 FB 54 65 92 11 02 28 F9 \nExponent: 01 00 01', 'Signature Length: 256 bytes / 2048 bits\nSignature: 00 01 02 39 91 21 36 53 5A 8A 26 00 E3 EF 35 4B B0 E3 8F 0A \n           61 86 5B 4D 31 AA 27 ED 62 32 03 92 0F 8B 32 75 97 05 86 A6 \n           F4 46 0A F7 57 15 C3 7E 90 AA 22 3D 44 7C 73 CF 24 A9 38 1A \n           EA 99 EC ED 64 2E 15 BB C1 23 36 BE 8A C7 08 F9 DD 92 79 C1 \n           A5 DD 78 8D 23 12 07 00 CC FD 1B 5C F6 4F 32 F7 BF 45 47 F0 \n           54 76 7D 5F E9 08 7D 79 1F 2C D7 F1 97 38 20 4A F1 DD 67 07 \n           02 CC 21 0C 35 5F CB F2 2D 8A 8B ED 27 BA C6 2C 61 55 1D 8B \n           4C EC 37 61 48 98 4C AE 85 D9 9F 40 5B 1E 40 3F BF 73 39 15 \n           C5 14 F5 54 F6 6C 09 5D C7 0A 5F 7F AD 2F 4F 1E 0F 2A 72 2E \n           57 0D 0A 1B 82 C3 FD 5C D1 5B E0 56 F7 A3 69 A9 3D 68 3A 25 \n           20 EA B3 65 1F 4B EB DF BF 3B E0 AE 3C 1C 63 A6 06 F6 FA 65 \n           BB 32 9F 38 1B 0D E7 93 0F E8 2C 25 84 64 B3 98 5E 88 75 A4 \n           35 4D E0 8C D4 98 1D D8 F3 EB 49 A5 24 B5 02 04 12', 'SHA-256 Fingerprint: 2D 92 9D F1 02 BC 72 C7 9E 82 88 25 6E 22 E8 B8 7B 6D 99 B2 \n                     E2 93 16 86 58 94 A1 63 AF B6 DF F1 \nSHA-1 Fingerprint: AC FF 91 A8 C8 4F A5 44 10 31 1C 1D 82 8A D2 0C 55 F9 B7 8F \nMD5 Fingerprint: 2E 42 72 80 1F BF C2 F4 1D C7 7A D3 9F CF 7D 7C']</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -19654,10 +19144,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H257" t="n">
+        <v>10000</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -19729,10 +19217,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H258" t="n">
+        <v>10000</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -19756,7 +19242,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>['Here is the list of SSL ciphers supported by the remote server :\nEach group is reported per SSL Version.', 'SSL Version : TLSv1.3\n  High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    TLS_AES_128_GCM_SHA256        0x13, 0x01       -             -        AES-GCM(128)           SHA256\n    TLS_AES_256_GCM_SHA384        0x13, 0x02       -             -        AES-GCM(256)           SHA384\n    TLS_CHACHA20_POLY1305_SHA256  0x13, 0x03       -             -        ChaCha20-Poly1305(256) SHA256', 'SSL Version : TLSv1.2\n  High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    ECDHE-RSA-AES128-SHA256       0xC0, 0x2F       ECDHE         RSA      AES-GCM(128)           SHA256\n    ECDHE-RSA-AES256-SHA384       0xC0, 0x30       ECDHE         RSA      AES-GCM(256)           SHA384\n    ECDHE-RSA-CHACHA20-POLY1305   0xCC, 0xA8       ECDHE         RSA      ChaCha20-Poly1305(256) SHA256\n    RSA-AES128-SHA256             0x00, 0x9C       RSA           RSA      AES-GCM(128)           SHA256\n    RSA-AES256-SHA384             0x00, 0x9D       RSA           RSA      AES-GCM(256)           SHA384\n    ECDHE-RSA-AES128-SHA          0xC0, 0x13       ECDHE         RSA      AES-CBC(128)           SHA1\n    ECDHE-RSA-AES128-SHA256       0xC0, 0x27       ECDHE         RSA      AES-CBC(128)           SHA256\n    ECDHE-RSA-AES256-SHA          0xC0, 0x14       ECDHE         RSA      AES-CBC(256)           SHA1\n    ECDHE-RSA-AES256-SHA384       0xC0, 0x28       ECDHE         RSA      AES-CBC(256)           SHA384\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    RSA-AES128-SHA256             0x00, 0x3C       RSA           RSA      AES-CBC(128)           SHA256\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RSA-AES256-SHA256             0x00, 0x3D       RSA           RSA      AES-CBC(256)           SHA256', 'The fields above are :', '{Tenable ciphername}\n  {Cipher ID code}\n  Kex={key exchange}\n  Auth={authentication}\n  Encrypt={symmetric encryption method}\n  MAC={message authentication code}\n  {export flag}']</t>
+          <t>['Here is the list of SSL ciphers supported by the remote server :\nEach group is reported per SSL Version.', 'SSL Version : TLSv1.3\n  High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    TLS_AES_128_GCM_SHA256        0x13, 0x01       -             -        AES-GCM(128)           SHA256\n    TLS_AES_256_GCM_SHA384        0x13, 0x02       -             -        AES-GCM(256)           SHA384\n    TLS_CHACHA20_POLY1305_SHA256  0x13, 0x03       -             -        ChaCha20-Poly1305(256) SHA256', 'SSL Version : TLSv1.2\n  High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    ECDHE-RSA-AES128-SHA256       0xC0, 0x2F       ECDHE         RSA      AES-GCM(128)           SHA256\n    ECDHE-RSA-AES256-SHA384       0xC0, 0x30       ECDHE         RSA      AES-GCM(256)           SHA384\n    ECDHE-RSA-CHACHA20-POLY1305   0xCC, 0xA8       ECDHE         RSA      ChaCha20-Poly1305(256) SHA256\n    RSA-AES128-SHA256             0x00, 0x9C       RSA           RSA      AES-GCM(128)           SHA256\n    RSA-AES256-SHA384             0x00, 0x9D       RSA           RSA      AES-GCM(256)           SHA384\n    ECDHE-RSA-AES128-SHA          0xC0, 0x13       ECDHE         RSA      AES-CBC(128)           SHA1\n    ECDHE-RSA-AES128-SHA256       0xC0, 0x27       ECDHE         RSA      AES-CBC(128)           SHA256\n    ECDHE-RSA-AES256-SHA          0xC0, 0x14       ECDHE         RSA      AES-CBC(256)           SHA1\n    ECDHE-RSA-AES256-SHA384       0xC0, 0x28       ECDHE         RSA      AES-CBC(256)           SHA384\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    RSA-AES128-SHA256             0x00, 0x3C       RSA           RSA      AES-CBC(128)           SHA256\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RSA-AES256-SHA256             0x00, 0x3D       RSA           RSA      AES-CBC(256)           SHA256']</t>
         </is>
       </c>
       <c r="N258" t="n">
@@ -19804,10 +19290,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H259" t="n">
+        <v>10000</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -19879,10 +19363,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H260" t="n">
+        <v>10000</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -19954,10 +19436,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H261" t="n">
+        <v>10000</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -20029,10 +19509,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H262" t="n">
+        <v>10000</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -20104,10 +19582,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H263" t="n">
+        <v>0</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -20179,10 +19655,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H264" t="n">
+        <v>0</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -20254,10 +19728,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H265" t="n">
+        <v>10000</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -20329,10 +19801,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H266" t="n">
+        <v>10000</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -20404,10 +19874,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H267" t="n">
+        <v>10000</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -20479,10 +19947,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H268" t="n">
+        <v>0</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -20554,10 +20020,8 @@
           <t>172.31.1.101</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="H269" t="n">
+        <v>10000</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>

--- a/resources/nessus/Nessus_VulnLab_scan-b.xlsx
+++ b/resources/nessus/Nessus_VulnLab_scan-b.xlsx
@@ -509,11 +509,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -562,7 +558,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -582,11 +578,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -635,7 +627,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -655,11 +647,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -688,11 +676,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -708,7 +692,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -728,16 +712,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -761,11 +737,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -781,7 +753,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -801,16 +773,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -834,11 +798,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -854,7 +814,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -874,16 +834,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -907,11 +859,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -927,7 +875,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -947,16 +895,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -980,11 +920,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -1000,7 +936,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -1020,16 +956,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1053,11 +981,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -1073,7 +997,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -1093,16 +1017,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1126,11 +1042,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -1146,7 +1058,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -1166,16 +1078,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1199,11 +1103,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -1219,7 +1119,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -1239,11 +1139,7 @@
           <t>['Limit incoming traffic to this port if desired.']</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>['https://www.postgresql.org/']</t>
@@ -1272,11 +1168,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>['The remote service is a PostgreSQL database server, or a derivative such as EnterpriseDB.']</t>
@@ -1292,7 +1184,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{"plugin_id": 26024, "publication_date": "2007/09/14", "modification_date": "2025/09/24"}</t>
+          <t>{"publication_date": "2007/09/14", "modification_date": "2025/09/24", "family": null, "severity": null, "plugin_id": 26024}</t>
         </is>
       </c>
     </row>
@@ -1312,11 +1204,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -1345,27 +1233,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>25220</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -1385,16 +1265,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1418,11 +1290,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -1438,7 +1306,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1326,7 @@
           <t>['Enable authentication or restrict access to the MongoDB service.']</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>['https://www.mongodb.com/']</t>
@@ -1511,7 +1375,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{"plugin_id": 81777, "publication_date": "2015/03/12", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2015/03/12", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 81777}</t>
         </is>
       </c>
     </row>
@@ -1531,11 +1395,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -1584,7 +1444,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -1604,11 +1464,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -1657,7 +1513,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -1677,11 +1533,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -1710,11 +1562,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -1730,7 +1578,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -1750,16 +1598,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1783,11 +1623,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -1803,7 +1639,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -1823,16 +1659,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1856,11 +1684,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -1876,7 +1700,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -1896,16 +1720,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1929,11 +1745,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -1949,7 +1761,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -1969,11 +1781,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>['https://www.mongodb.com/']</t>
@@ -2002,11 +1810,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>['A document-oriented database system is listening on the remote port.']</t>
@@ -2022,7 +1826,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>{"plugin_id": 65914, "publication_date": "2013/04/10", "modification_date": "2025/09/24"}</t>
+          <t>{"publication_date": "2013/04/10", "modification_date": "2025/09/24", "family": null, "severity": null, "plugin_id": 65914}</t>
         </is>
       </c>
     </row>
@@ -2042,16 +1846,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2075,11 +1871,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -2095,7 +1887,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -2115,16 +1907,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2148,11 +1932,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -2168,7 +1948,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -2188,16 +1968,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2221,11 +1993,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -2241,7 +2009,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -2261,16 +2029,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2294,11 +2054,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -2314,7 +2070,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -2334,16 +2090,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2367,11 +2115,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -2387,7 +2131,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2151,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -2440,27 +2180,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>25220</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -2480,16 +2212,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2513,11 +2237,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -2533,7 +2253,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2273,7 @@
           <t>["Enable the 'requirepass' directive in the redis.conf configuration file."]</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>['https://redis.io/commands/auth']</t>
@@ -2606,7 +2322,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>{"plugin_id": 100634, "publication_date": "2017/06/06", "modification_date": "2022/04/11"}</t>
+          <t>{"publication_date": "2017/06/06", "modification_date": "2022/04/11", "family": null, "severity": null, "plugin_id": 100634}</t>
         </is>
       </c>
     </row>
@@ -2626,11 +2342,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -2679,7 +2391,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -2699,11 +2411,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -2752,7 +2460,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -2772,11 +2480,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -2805,11 +2509,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -2825,7 +2525,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2545,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2878,11 +2570,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -2898,7 +2586,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -2918,16 +2606,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -2951,11 +2631,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -2971,7 +2647,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -2991,16 +2667,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3024,11 +2692,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -3044,7 +2708,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -3064,11 +2728,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>['https://redis.io']</t>
@@ -3097,11 +2757,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>['Redis, a document-oriented database system, is running on the remote host.']</t>
@@ -3117,7 +2773,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>{"plugin_id": 100635, "publication_date": "2017/06/06", "modification_date": "2025/09/29"}</t>
+          <t>{"publication_date": "2017/06/06", "modification_date": "2025/09/29", "family": null, "severity": null, "plugin_id": 100635}</t>
         </is>
       </c>
     </row>
@@ -3137,16 +2793,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3170,11 +2818,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -3190,7 +2834,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -3210,11 +2854,7 @@
           <t>["If you are not concerned about such behavior, enable the 'Scan Network Printers' setting under the 'Do not scan fragile devices'\nadvanced settings block and re-run the scan."]</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>['XREF IAVB:0001-B-0525']</t>
@@ -3243,11 +2883,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>["The remote host appears to be a network printer or multi-function device that supports the AppSocket (also known as JetDirect) protocol. Such devices often react very poorly when scanned - some crash, others print a number of pages.  To avoid problems, Nessus has marked the remote host as 'Dead' and will not scan it,  beyond minimal probing traffic that allows the scanner to identify it as a host to be excluded."]</t>
@@ -3263,7 +2899,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>{"plugin_id": 44920, "publication_date": "2010/02/26", "modification_date": "2025/08/06"}</t>
+          <t>{"publication_date": "2010/02/26", "modification_date": "2025/08/06", "family": null, "severity": null, "plugin_id": 44920}</t>
         </is>
       </c>
     </row>
@@ -3283,16 +2919,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3316,11 +2944,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -3336,7 +2960,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -3356,16 +2980,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3389,11 +3005,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -3409,7 +3021,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -3429,11 +3041,7 @@
           <t>['Upgrade to CouchDB 3.1.2 and apply the recommended settings, or upgrade to 3.2.0 or later.']</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>['https://docs.couchdb.org/en/stable/cve/2021-38295.html', 'CVE CVE-2021-38295']</t>
@@ -3482,7 +3090,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>{"plugin_id": 182208, "publication_date": "2023/09/29", "modification_date": "2023/10/02"}</t>
+          <t>{"publication_date": "2023/09/29", "modification_date": "2023/10/02", "family": null, "severity": null, "plugin_id": 182208}</t>
         </is>
       </c>
     </row>
@@ -3502,11 +3110,7 @@
           <t>['Secure the CouchDB installation with an administrative account.']</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>['http://books.couchdb.org/relax/reference/security']</t>
@@ -3555,7 +3159,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45434, "publication_date": "2010/04/07", "modification_date": "2017/12/01"}</t>
+          <t>{"publication_date": "2010/04/07", "modification_date": "2017/12/01", "family": null, "severity": null, "plugin_id": 45434}</t>
         </is>
       </c>
     </row>
@@ -3575,11 +3179,7 @@
           <t>['Upgrade to CouchDB 3.2.3, 3.3.2 or later.']</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>['https://docs.couchdb.org/en/latest/cve/2023-26268.html', 'CVE CVE-2023-26268', 'XREF IAVB:2023-B-0030-S']</t>
@@ -3628,7 +3228,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>{"plugin_id": 175115, "publication_date": "2023/05/04", "modification_date": "2023/12/15"}</t>
+          <t>{"publication_date": "2023/05/04", "modification_date": "2023/12/15", "family": null, "severity": null, "plugin_id": 175115}</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3248,7 @@
           <t>['Upgrade to CouchDB 3.3.3 or later.']</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>['https://docs.couchdb.org/en/stable/cve/2023-45725.html', 'CVE CVE-2023-45725', 'XREF IAVB:2023-B-0099']</t>
@@ -3701,7 +3297,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>{"plugin_id": 186916, "publication_date": "2023/12/14", "modification_date": "2023/12/21"}</t>
+          <t>{"publication_date": "2023/12/14", "modification_date": "2023/12/21", "family": null, "severity": null, "plugin_id": 186916}</t>
         </is>
       </c>
     </row>
@@ -3721,11 +3317,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -3774,7 +3366,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -3794,11 +3386,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -3847,7 +3435,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -3867,11 +3455,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>['http://couchdb.apache.org/', 'XREF IAVT:0001-T-0529']</t>
@@ -3900,11 +3484,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>['The remote server is running CouchDB, a document-oriented database system written in Erlang.']</t>
@@ -3920,7 +3500,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{"plugin_id": 51922, "publication_date": "2011/02/09", "modification_date": "2020/09/22"}</t>
+          <t>{"publication_date": "2011/02/09", "modification_date": "2020/09/22", "family": null, "severity": null, "plugin_id": 51922}</t>
         </is>
       </c>
     </row>
@@ -3940,11 +3520,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -3973,11 +3549,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -3993,7 +3565,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -4013,16 +3585,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4046,11 +3610,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -4066,7 +3626,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -4086,16 +3646,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4119,11 +3671,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -4139,7 +3687,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -4159,16 +3707,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4192,11 +3732,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -4212,7 +3748,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -4232,16 +3768,8 @@
           <t>['Install the patches listed below.']</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4265,11 +3793,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>['The remote host is missing one or more security patches. This plugin lists the newest version of each patch to install to make sure the remote host is up-to-date.', "Note: Because the 'Show missing patches that have been superseded' setting in your scan policy depends on this plugin, it will always run and cannot be disabled."]</t>
@@ -4285,7 +3809,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{"plugin_id": 66334, "publication_date": "2013/07/08", "modification_date": "2026/07/17"}</t>
+          <t>{"publication_date": "2013/07/08", "modification_date": "2026/07/17", "family": null, "severity": null, "plugin_id": 66334}</t>
         </is>
       </c>
     </row>
@@ -4305,16 +3829,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4338,11 +3854,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -4358,7 +3870,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -4378,11 +3890,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -4431,7 +3939,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -4451,11 +3959,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -4504,7 +4008,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -4524,11 +4028,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -4557,11 +4057,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -4577,7 +4073,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -4597,16 +4093,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4630,11 +4118,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -4650,7 +4134,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4154,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4703,11 +4179,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -4723,7 +4195,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -4743,11 +4215,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0931']</t>
@@ -4776,11 +4244,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>['This plugin attempts to determine the type and the version of the   remote web server.']</t>
@@ -4796,7 +4260,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10107, "publication_date": "2000/01/04", "modification_date": "2020/10/30"}</t>
+          <t>{"publication_date": "2000/01/04", "modification_date": "2020/10/30", "family": null, "severity": null, "plugin_id": 10107}</t>
         </is>
       </c>
     </row>
@@ -4816,16 +4280,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4849,11 +4305,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -4869,7 +4321,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -4889,16 +4341,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4922,11 +4366,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>['This test gives some information about the remote HTTP protocol - the version used, whether HTTP Keep-Alive is enabled, etc...', 'This test is informational only and does not denote any security problem.']</t>
@@ -4942,7 +4382,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>{"plugin_id": 24260, "publication_date": "2007/01/30", "modification_date": "2024/02/26"}</t>
+          <t>{"publication_date": "2007/01/30", "modification_date": "2024/02/26", "family": null, "severity": null, "plugin_id": 24260}</t>
         </is>
       </c>
     </row>
@@ -4962,16 +4402,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -4995,11 +4427,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -5015,7 +4443,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -5035,16 +4463,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5068,11 +4488,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -5088,7 +4504,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -5108,16 +4524,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5141,11 +4549,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -5161,7 +4565,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -5181,16 +4585,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5214,11 +4610,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -5234,7 +4626,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -5254,16 +4646,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5287,11 +4671,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -5307,7 +4687,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -5327,16 +4707,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5360,11 +4732,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>['The remote host is running the Squid proxy server, an open source proxy server. It was possible to read the version number from the banner.']</t>
@@ -5380,7 +4748,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>{"plugin_id": 49692, "publication_date": "2010/09/28", "modification_date": "2024/06/17"}</t>
+          <t>{"publication_date": "2010/09/28", "modification_date": "2024/06/17", "family": null, "severity": null, "plugin_id": 49692}</t>
         </is>
       </c>
     </row>
@@ -5400,11 +4768,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -5433,27 +4797,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>25220</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -5473,16 +4829,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5506,11 +4854,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -5526,7 +4870,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -5546,16 +4890,8 @@
           <t>['Disable cleartext authentication mechanisms in the AMQP configuration.']</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5589,17 +4925,13 @@
           <t>['The remote Advanced Message Queuing Protocol (AMQP) service supports one or more authentication mechanisms that allow credentials to be sent in the clear.']</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>87733</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>{"plugin_id": 87733, "publication_date": "2016/01/05", "modification_date": "2016/01/05"}</t>
+          <t>{"publication_date": "2016/01/05", "modification_date": "2016/01/05", "family": null, "severity": null, "plugin_id": 87733}</t>
         </is>
       </c>
     </row>
@@ -5619,11 +4951,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -5672,7 +5000,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -5692,11 +5020,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -5745,7 +5069,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -5765,11 +5089,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>['http://www.amqp.org/', 'http://www.rabbitmq.com/resources/specs/amqp0-9-1.pdf', 'http://www.nessus.org/u?388dd79c']</t>
@@ -5798,11 +5118,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>['The remote host is running an AMQP server, which provides messaging and queuing services for other applications.']</t>
@@ -5818,7 +5134,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{"plugin_id": 62349, "publication_date": "2012/09/27", "modification_date": "2022/04/11"}</t>
+          <t>{"publication_date": "2012/09/27", "modification_date": "2022/04/11", "family": null, "severity": null, "plugin_id": 62349}</t>
         </is>
       </c>
     </row>
@@ -5838,11 +5154,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -5871,11 +5183,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -5891,7 +5199,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -5911,16 +5219,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -5944,11 +5244,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -5964,7 +5260,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -5984,11 +5280,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>['http://erlang.org/doc/man/epmd.html', 'http://erlang.org/doc/apps/erts/erl_dist_protocol.html']</t>
@@ -6017,27 +5309,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>['The remote host is running Erlang Port Mapper Daemon, which acts as a name server on all hosts involved in distributed Erlang computations.']</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
         <v>62351</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{"plugin_id": 62351, "publication_date": "2012/09/27", "modification_date": "2022/04/11"}</t>
+          <t>{"publication_date": "2012/09/27", "modification_date": "2022/04/11", "family": null, "severity": null, "plugin_id": 62351}</t>
         </is>
       </c>
     </row>
@@ -6057,16 +5341,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6090,11 +5366,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -6110,7 +5382,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -6130,16 +5402,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6163,11 +5427,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -6183,7 +5443,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -6203,16 +5463,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6236,11 +5488,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -6256,7 +5504,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -6276,16 +5524,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6309,11 +5549,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -6329,7 +5565,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -6349,16 +5585,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6382,11 +5610,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -6402,7 +5626,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -6422,16 +5646,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6455,11 +5671,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -6475,7 +5687,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -6495,11 +5707,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>['https://www.rabbitmq.com/', 'XREF IAVT:0001-T-0703']</t>
@@ -6528,11 +5736,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>['Pivotal RabbitMQ server with the Management plugin is running on the remote host. RabbitMQ is a message broker application that uses AMQP for communications, and the Management plugin uses HTTP for managing the broker.']</t>
@@ -6548,7 +5752,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>{"plugin_id": 100297, "publication_date": "2017/05/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2017/05/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 100297}</t>
         </is>
       </c>
     </row>
@@ -6568,11 +5772,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -6601,27 +5801,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
         <v>25220</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -6641,16 +5833,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6674,11 +5858,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -6694,7 +5874,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -6714,11 +5894,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -6767,7 +5943,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -6787,11 +5963,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -6840,7 +6012,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -6860,11 +6032,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -6893,11 +6061,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -6913,7 +6077,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -6933,16 +6097,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -6966,11 +6122,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -6986,7 +6138,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -7006,16 +6158,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7039,11 +6183,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -7059,7 +6199,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -7079,16 +6219,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7112,11 +6244,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -7132,7 +6260,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -7152,16 +6280,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7185,11 +6305,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -7205,7 +6321,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -7225,16 +6341,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7258,11 +6366,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -7278,7 +6382,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -7298,16 +6402,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7331,11 +6427,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -7351,7 +6443,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -7371,16 +6463,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7404,11 +6488,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -7424,7 +6504,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -7444,11 +6524,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -7477,27 +6553,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
         <v>25220</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -7517,16 +6585,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -7550,11 +6610,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -7570,7 +6626,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -7590,11 +6646,7 @@
           <t>["If memcached is deployed in untrusted networks, it's recommended that SASL be enabled to restrict access to authorized users."]</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>['http://memcached.org/', 'https://code.google.com/archive/p/memcached', 'https://www.mediawiki.org/wiki/Memcached']</t>
@@ -7623,11 +6675,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>['memcached, a memory-based object store, is listening on the remote port.']</t>
@@ -7643,7 +6691,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>{"plugin_id": 26197, "publication_date": "2007/10/02", "modification_date": "2019/11/22"}</t>
+          <t>{"publication_date": "2007/10/02", "modification_date": "2019/11/22", "family": null, "severity": null, "plugin_id": 26197}</t>
         </is>
       </c>
     </row>
@@ -7663,11 +6711,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -7716,7 +6760,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -7736,11 +6780,7 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>['https://www.itu.int/rec/T-REC-X.509/en', 'https://en.wikipedia.org/wiki/X.509']</t>
@@ -7789,7 +6829,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>{"plugin_id": 51192, "publication_date": "2010/12/15", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2010/12/15", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 51192}</t>
         </is>
       </c>
     </row>
@@ -7809,16 +6849,8 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -7862,7 +6894,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57582, "publication_date": "2012/01/17", "modification_date": "2022/06/14"}</t>
+          <t>{"publication_date": "2012/01/17", "modification_date": "2022/06/14", "family": null, "severity": null, "plugin_id": 57582}</t>
         </is>
       </c>
     </row>
@@ -7882,11 +6914,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -7935,7 +6963,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -7955,11 +6983,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -7988,11 +7012,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -8008,7 +7028,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -8028,16 +7048,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8061,11 +7073,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -8081,7 +7089,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -8101,16 +7109,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8134,11 +7134,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -8154,7 +7150,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -8174,16 +7170,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8207,11 +7195,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -8227,7 +7211,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -8247,16 +7231,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8280,11 +7256,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>["By sending a search request with a filter set to 'objectClass=*', it is possible to extract information about the remote LDAP server."]</t>
@@ -8300,7 +7272,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25701, "publication_date": "2007/07/12", "modification_date": "2022/09/28"}</t>
+          <t>{"publication_date": "2007/07/12", "modification_date": "2022/09/28", "family": null, "severity": null, "plugin_id": 25701}</t>
         </is>
       </c>
     </row>
@@ -8320,11 +7292,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>['https://en.wikipedia.org/wiki/LDAP']</t>
@@ -8353,27 +7321,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>['The remote host is running a Lightweight Directory Access Protocol (LDAP) server. LDAP is a protocol for providing access to directory services over TCP/IP.']</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
         <v>20870</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>{"plugin_id": 20870, "publication_date": "2006/02/10", "modification_date": "2022/09/29"}</t>
+          <t>{"publication_date": "2006/02/10", "modification_date": "2022/09/29", "family": null, "severity": null, "plugin_id": 20870}</t>
         </is>
       </c>
     </row>
@@ -8393,11 +7353,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>['https://en.wikipedia.org/wiki/STARTTLS', 'https://tools.ietf.org/html/rfc2830']</t>
@@ -8426,11 +7382,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>["The remote LDAP service supports the use of the 'STARTTLS' command to switch from a cleartext to an encrypted communications channel."]</t>
@@ -8446,7 +7398,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>{"plugin_id": 42329, "publication_date": "2009/10/30", "modification_date": "2021/02/24"}</t>
+          <t>{"publication_date": "2009/10/30", "modification_date": "2021/02/24", "family": null, "severity": null, "plugin_id": 42329}</t>
         </is>
       </c>
     </row>
@@ -8466,16 +7418,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8499,11 +7443,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -8519,7 +7459,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -8539,16 +7479,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8572,11 +7504,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -8592,7 +7520,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -8612,16 +7540,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8645,11 +7565,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -8665,7 +7581,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -8685,16 +7601,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8718,11 +7626,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -8738,7 +7642,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -8758,16 +7662,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8791,11 +7687,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -8811,7 +7703,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -8831,11 +7723,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?7a390f87', 'http://www.nessus.org/u?ad7d6b3b', 'http://www.nessus.org/u?1c0c61e0', 'http://www.nessus.org/u?5eec4b28']</t>
@@ -8864,11 +7752,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>['This plugin reports network services that do not offer post-quantum ciphers.  Tenable makes no attempt to determine whether the remote service would be vulnerable to a post-quantum attack.', "However, cryptography that depends on the classic difficulty of solving the discrete logarithm problem or on the classic difficulty of large prime factorization is broken by Shor's algorithm.  Examples of this are RSA asymmetric encryption and Diffie-Hellman key exchange."]</t>
@@ -8884,7 +7768,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277650, "publication_date": "2025/12/08", "modification_date": "2025/12/08"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2025/12/08", "family": null, "severity": null, "plugin_id": 277650}</t>
         </is>
       </c>
     </row>
@@ -8904,16 +7788,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8937,11 +7813,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL and TLS versions are supported by the remote service for encrypting communications.']</t>
@@ -8957,7 +7829,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{"plugin_id": 56984, "publication_date": "2011/12/01", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2011/12/01", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 56984}</t>
         </is>
       </c>
     </row>
@@ -8977,16 +7849,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9010,11 +7874,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>['This plugin connects to every SSL-related port and attempts to extract and dump the X.509 certificate.']</t>
@@ -9030,7 +7890,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10863, "publication_date": "2008/05/19", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2008/05/19", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 10863}</t>
         </is>
       </c>
     </row>
@@ -9050,11 +7910,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'http://www.nessus.org/u?cc4a822a', 'https://www.openssl.org/~bodo/tls-cbc.txt']</t>
@@ -9083,11 +7939,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>['The remote host supports the use of SSL ciphers that operate in Cipher Block Chaining (CBC) mode.  These cipher suites offer additional security over Electronic Codebook (ECB) mode, but have the potential to leak information if used improperly.']</t>
@@ -9103,7 +7955,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{"plugin_id": 70544, "publication_date": "2013/10/22", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2013/10/22", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 70544}</t>
         </is>
       </c>
     </row>
@@ -9123,11 +7975,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/man1.0.2/man1/ciphers.html', 'http://www.nessus.org/u?e17ffced']</t>
@@ -9156,11 +8004,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL ciphers are supported by the remote service for encrypting communications.']</t>
@@ -9176,7 +8020,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{"plugin_id": 21643, "publication_date": "2006/06/05", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2006/06/05", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 21643}</t>
         </is>
       </c>
     </row>
@@ -9196,11 +8040,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'https://en.wikipedia.org/wiki/Diffie-Hellman_key_exchange', 'https://en.wikipedia.org/wiki/Perfect_forward_secrecy']</t>
@@ -9229,11 +8069,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>["The remote host supports the use of SSL ciphers that offer Perfect Forward Secrecy (PFS) encryption.  These cipher suites ensure that recorded SSL traffic cannot be broken at a future date if the server's private key is compromised."]</t>
@@ -9249,7 +8085,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57041, "publication_date": "2011/12/07", "modification_date": "2021/03/09"}</t>
+          <t>{"publication_date": "2011/12/07", "modification_date": "2021/03/09", "family": null, "severity": null, "plugin_id": 57041}</t>
         </is>
       </c>
     </row>
@@ -9269,11 +8105,7 @@
           <t>["Ensure that use of this root Certification Authority certificate complies with your organization's acceptable use and security policies."]</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>['https://docs.microsoft.com/en-us/previous-versions/windows/it-pro/windows-server-2003/cc778623(v=ws.10)']</t>
@@ -9302,11 +8134,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>['The remote service uses an SSL certificate chain that contains a self-signed root Certification Authority certificate at the top of the chain.']</t>
@@ -9322,7 +8150,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>{"plugin_id": 94761, "publication_date": "2016/11/14", "modification_date": "2018/11/15"}</t>
+          <t>{"publication_date": "2016/11/14", "modification_date": "2018/11/15", "family": null, "severity": null, "plugin_id": 94761}</t>
         </is>
       </c>
     </row>
@@ -9342,11 +8170,7 @@
           <t>['Only enable support for recommened cipher suites.']</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>['https://wiki.mozilla.org/Security/Server_Side_TLS', 'https://ssl-config.mozilla.org/']</t>
@@ -9375,11 +8199,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>['The remote host has open SSL/TLS ports which advertise discouraged cipher suites. It is recommended to only enable support for the following cipher suites:', 'TLSv1.3:\n  - 0x13,0x01 TLS13_AES_128_GCM_SHA256\n  - 0x13,0x02 TLS13_AES_256_GCM_SHA384\n  - 0x13,0x03 TLS13_CHACHA20_POLY1305_SHA256', 'TLSv1.2:\n  - 0xC0,0x2B ECDHE-ECDSA-AES128-GCM-SHA256\n  - 0xC0,0x2F ECDHE-RSA-AES128-GCM-SHA256\n  - 0xC0,0x2C ECDHE-ECDSA-AES256-GCM-SHA384\n  - 0xC0,0x30 ECDHE-RSA-AES256-GCM-SHA384\n  - 0xCC,0xA9 ECDHE-ECDSA-CHACHA20-POLY1305\n  - 0xCC,0xA8 ECDHE-RSA-CHACHA20-POLY1305', 'This is the recommended configuration for the vast majority of services, as it is highly secure and compatible with nearly every client released in the last five (or more) years.']</t>
@@ -9395,7 +8215,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>{"plugin_id": 156899, "publication_date": "2022/01/20", "modification_date": "2024/02/12"}</t>
+          <t>{"publication_date": "2022/01/20", "modification_date": "2024/02/12", "family": null, "severity": null, "plugin_id": 156899}</t>
         </is>
       </c>
     </row>
@@ -9415,11 +8235,7 @@
           <t>['Replace affected ciphers with algorithms chosen to resist CRQC attack.']</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?54fba2c1']</t>
@@ -9448,11 +8264,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>["This plugin reports network services that may be vulnerable now to a future attack by adversaries using a cryptographically relevant quantum computer (CRQC). Shor's is a theoretical algorithm that leverages the unique ability of quantum computation to do massively parallel calculations developed by Peter Shor in 1994.", "This algorithm easily computes two classically difficult mathematical problems used in modern cryptography; discrete logarithms, and factoring numbers formed by multiplying large primes.  Shor's reduces both of these problems from taking exponential time in chosen cases to being solvable in polynomial time.", "Asymmetric encryption algorithms such as RSA, Diffie-Hellman and Elliptic Curve Diffie-Hellman are impacted by Shor's Algorithm.  The most common uses of these algorithms are in symmetric key establishment and authentication.  These uses render Shor's Algorithm particularly dangerous because it may give an adversary the ability to harvest network communications now, and in the future, when a CRQC becomes available, extract the symmetric key and decrypt the communication."]</t>
@@ -9468,7 +8280,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>{"plugin_id": 298387, "publication_date": "2026/02/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2026/02/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 298387}</t>
         </is>
       </c>
     </row>
@@ -9488,11 +8300,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -9521,27 +8329,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
         <v>25220</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -9561,16 +8361,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9594,11 +8386,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>['This plugin detects which TLS supported groups entries are supported by the remote service.']</t>
@@ -9614,7 +8402,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277654, "publication_date": "2025/12/08", "modification_date": "2026/06/15"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2026/06/15", "family": null, "severity": null, "plugin_id": 277654}</t>
         </is>
       </c>
     </row>
@@ -9634,11 +8422,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc5246']</t>
@@ -9667,11 +8451,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.2.']</t>
@@ -9687,7 +8467,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{"plugin_id": 136318, "publication_date": "2020/05/04", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/05/04", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 136318}</t>
         </is>
       </c>
     </row>
@@ -9707,16 +8487,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9740,11 +8512,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -9760,7 +8528,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -9780,11 +8548,7 @@
           <t>['Update the AJP configuration to require authorization and/or upgrade the Tomcat server to 7.0.100, 8.5.51, 9.0.31 or later.']</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?8ebe6246', 'http://www.nessus.org/u?4e287adb', 'http://www.nessus.org/u?cbc3d54e', 'https://access.redhat.com/security/cve/CVE-2020-1745', 'https://access.redhat.com/solutions/4851251', 'http://www.nessus.org/u?dd218234', 'http://www.nessus.org/u?dd772531', 'http://www.nessus.org/u?2a01d6bf', 'http://www.nessus.org/u?3b5af27e', 'http://www.nessus.org/u?9dab109f', 'http://www.nessus.org/u?5eafcf70', 'CVE CVE-2020-1745', 'CVE CVE-2020-1938', 'XREF CISA-KNOWN-EXPLOITED:2022/03/17', 'XREF CEA-ID:CEA-2020-0021']</t>
@@ -9833,7 +8597,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{"plugin_id": 134862, "publication_date": "2020/03/24", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2020/03/24", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 134862}</t>
         </is>
       </c>
     </row>
@@ -9853,11 +8617,7 @@
           <t>['Upgrade to a version of Apache Tomcat that is currently supported.']</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>['https://tomcat.apache.org/tomcat-60-eol.html']</t>
@@ -9906,7 +8666,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{"plugin_id": 171349, "publication_date": "2023/02/10", "modification_date": "2024/05/06"}</t>
+          <t>{"publication_date": "2023/02/10", "modification_date": "2024/05/06", "family": null, "severity": null, "plugin_id": 171349}</t>
         </is>
       </c>
     </row>
@@ -9926,11 +8686,7 @@
           <t>['Delete the default index page and remove the example JSP and servlets. Follow the Tomcat or OWASP instructions to replace or modify the default error page.']</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?4cb3b4dd', 'https://www.owasp.org/index.php/Securing_tomcat']</t>
@@ -9979,7 +8735,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12085, "publication_date": "2004/03/02", "modification_date": "2024/09/03"}</t>
+          <t>{"publication_date": "2004/03/02", "modification_date": "2024/09/03", "family": null, "severity": null, "plugin_id": 12085}</t>
         </is>
       </c>
     </row>
@@ -9999,11 +8755,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -10052,7 +8804,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -10072,11 +8824,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -10125,7 +8873,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -10145,11 +8893,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>['http://tomcat.apache.org/connectors-doc/', 'http://tomcat.apache.org/connectors-doc/ajp/ajpv13a.html']</t>
@@ -10178,11 +8922,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>['The remote host is running an AJP (Apache JServ Protocol) connector, a service by which a standalone web server such as Apache communicates over TCP with a Java servlet container such as Tomcat.']</t>
@@ -10198,7 +8938,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{"plugin_id": 21186, "publication_date": "2006/04/05", "modification_date": "2019/11/22"}</t>
+          <t>{"publication_date": "2006/04/05", "modification_date": "2019/11/22", "family": null, "severity": null, "plugin_id": 21186}</t>
         </is>
       </c>
     </row>
@@ -10218,11 +8958,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>['https://tomcat.apache.org/', 'XREF IAVT:0001-T-0535']</t>
@@ -10251,11 +8987,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>['Nessus was able to detect a remote Apache Tomcat web server.', 'NOTE: When paranoia levels are elevated, this plugin will also consider versions obtained from responses with non-200 HTTP status codes.']</t>
@@ -10271,7 +9003,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{"plugin_id": 39446, "publication_date": "2009/06/18", "modification_date": "2026/01/22"}</t>
+          <t>{"publication_date": "2009/06/18", "modification_date": "2026/01/22", "family": null, "severity": null, "plugin_id": 39446}</t>
         </is>
       </c>
     </row>
@@ -10291,11 +9023,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -10324,11 +9052,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -10344,7 +9068,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -10364,16 +9088,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10397,11 +9113,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -10417,7 +9129,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -10437,16 +9149,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10470,11 +9174,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -10490,7 +9190,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -10510,11 +9210,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?d9c03a9a', 'http://www.nessus.org/u?b019cbdb', 'https://www.owasp.org/index.php/Test_HTTP_Methods_(OTG-CONFIG-006)']</t>
@@ -10543,11 +9239,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>['By calling the OPTIONS method, it is possible to determine which HTTP methods are allowed on each directory.', 'The following HTTP methods are considered insecure:\n  PUT, DELETE, CONNECT, TRACE, HEAD', "Many frameworks and languages treat 'HEAD' as a 'GET' request, albeit one without any body in the response. If a security constraint was set on 'GET' requests such that only 'authenticatedUsers' could access GET requests for a particular servlet or resource, it would be bypassed for the 'HEAD' version. This allowed unauthorized blind submission of any privileged GET request.", "As this list may be incomplete, the plugin also tests - if 'Thorough tests' are enabled or 'Enable web applications tests' is set to 'yes'\nin the scan policy - various known HTTP methods on each directory and considers them as unsupported if it receives a response code of 400, 403, 405, or 501.", 'Note that the plugin output is only informational and does not necessarily indicate the presence of any security vulnerabilities.']</t>
@@ -10563,7 +9255,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{"plugin_id": 43111, "publication_date": "2009/12/10", "modification_date": "2022/04/11"}</t>
+          <t>{"publication_date": "2009/12/10", "modification_date": "2022/04/11", "family": null, "severity": null, "plugin_id": 43111}</t>
         </is>
       </c>
     </row>
@@ -10583,11 +9275,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0931']</t>
@@ -10616,11 +9304,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>['This plugin attempts to determine the type and the version of the   remote web server.']</t>
@@ -10636,7 +9320,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10107, "publication_date": "2000/01/04", "modification_date": "2020/10/30"}</t>
+          <t>{"publication_date": "2000/01/04", "modification_date": "2020/10/30", "family": null, "severity": null, "plugin_id": 10107}</t>
         </is>
       </c>
     </row>
@@ -10656,16 +9340,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10689,11 +9365,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -10709,7 +9381,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -10729,16 +9401,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10762,11 +9426,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>['This test gives some information about the remote HTTP protocol - the version used, whether HTTP Keep-Alive is enabled, etc...', 'This test is informational only and does not denote any security problem.']</t>
@@ -10782,7 +9442,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{"plugin_id": 24260, "publication_date": "2007/01/30", "modification_date": "2024/02/26"}</t>
+          <t>{"publication_date": "2007/01/30", "modification_date": "2024/02/26", "family": null, "severity": null, "plugin_id": 24260}</t>
         </is>
       </c>
     </row>
@@ -10802,16 +9462,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10835,11 +9487,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -10855,7 +9503,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -10875,16 +9523,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10908,11 +9548,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -10928,7 +9564,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -10948,16 +9584,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -10981,11 +9609,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -11001,7 +9625,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -11021,16 +9645,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11054,11 +9670,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -11074,7 +9686,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -11094,16 +9706,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11127,11 +9731,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -11147,7 +9747,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -11167,16 +9767,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11200,11 +9792,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -11220,7 +9808,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -11240,11 +9828,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -11273,27 +9857,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
         <v>25220</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -11313,16 +9889,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11346,11 +9914,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -11366,7 +9930,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -11386,16 +9950,8 @@
           <t>["Remove the 'favicon.ico' file or create a custom one for your site."]</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11419,11 +9975,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>["The 'favicon.ico' file found on the remote web server belongs to a popular web server. This may be used to fingerprint the web server."]</t>
@@ -11439,7 +9991,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>{"plugin_id": 20108, "publication_date": "2005/10/28", "modification_date": "2020/06/12"}</t>
+          <t>{"publication_date": "2005/10/28", "modification_date": "2020/06/12", "family": null, "severity": null, "plugin_id": 20108}</t>
         </is>
       </c>
     </row>
@@ -11459,16 +10011,8 @@
           <t>['Disable this service if you do not use it.']</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11492,11 +10036,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>["The remote web server uses its default welcome page. Therefore, it's probable that this server is not used at all or is serving content that is meant to be hidden."]</t>
@@ -11512,7 +10052,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11422, "publication_date": "2003/03/20", "modification_date": "2018/08/15"}</t>
+          <t>{"publication_date": "2003/03/20", "modification_date": "2018/08/15", "family": null, "severity": null, "plugin_id": 11422}</t>
         </is>
       </c>
     </row>
@@ -11532,11 +10072,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -11585,7 +10121,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -11605,11 +10141,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -11658,7 +10190,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -11678,11 +10210,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -11711,11 +10239,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -11731,7 +10255,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -11751,16 +10275,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11784,11 +10300,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -11804,7 +10316,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -11824,16 +10336,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11857,11 +10361,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -11877,7 +10377,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -11897,16 +10397,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -11930,11 +10422,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -11950,7 +10438,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -11970,11 +10458,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0802']</t>
@@ -12003,11 +10487,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>['The remote host is running MySQL, an open source database server.']</t>
@@ -12023,7 +10503,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10719, "publication_date": "2001/08/13", "modification_date": "2025/09/24"}</t>
+          <t>{"publication_date": "2001/08/13", "modification_date": "2025/09/24", "family": null, "severity": null, "plugin_id": 10719}</t>
         </is>
       </c>
     </row>
@@ -12043,16 +10523,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12076,11 +10548,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -12096,7 +10564,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -12116,16 +10584,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12149,11 +10609,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -12169,7 +10625,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -12189,16 +10645,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12222,11 +10670,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -12242,7 +10686,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -12262,16 +10706,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12295,11 +10731,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -12315,7 +10747,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -12335,16 +10767,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12368,11 +10792,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>["It was possible to identify the remote service by its banner or by looking at the error message it sends when it receives a 'HELP'\nrequest."]</t>
@@ -12388,7 +10808,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11153, "publication_date": "2002/11/18", "modification_date": "2024/11/19"}</t>
+          <t>{"publication_date": "2002/11/18", "modification_date": "2024/11/19", "family": null, "severity": null, "plugin_id": 11153}</t>
         </is>
       </c>
     </row>
@@ -12408,11 +10828,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -12441,27 +10857,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
         <v>25220</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -12481,16 +10889,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12514,11 +10914,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -12534,7 +10930,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -12554,11 +10950,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -12607,7 +10999,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -12627,11 +11019,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -12680,7 +11068,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -12700,11 +11088,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -12733,11 +11117,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -12753,7 +11133,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -12773,16 +11153,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12806,11 +11178,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -12826,7 +11194,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -12846,16 +11214,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -12879,11 +11239,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -12899,7 +11255,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -12919,11 +11275,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0931']</t>
@@ -12952,11 +11304,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>['This plugin attempts to determine the type and the version of the   remote web server.']</t>
@@ -12972,7 +11320,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10107, "publication_date": "2000/01/04", "modification_date": "2020/10/30"}</t>
+          <t>{"publication_date": "2000/01/04", "modification_date": "2020/10/30", "family": null, "severity": null, "plugin_id": 10107}</t>
         </is>
       </c>
     </row>
@@ -12992,11 +11340,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0931']</t>
@@ -13025,11 +11369,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>['This plugin attempts to determine the type and the version of the   remote web server.']</t>
@@ -13045,7 +11385,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10107, "publication_date": "2000/01/04", "modification_date": "2020/10/30"}</t>
+          <t>{"publication_date": "2000/01/04", "modification_date": "2020/10/30", "family": null, "severity": null, "plugin_id": 10107}</t>
         </is>
       </c>
     </row>
@@ -13065,16 +11405,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13098,11 +11430,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -13118,7 +11446,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -13138,16 +11466,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13171,11 +11491,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>['This test gives some information about the remote HTTP protocol - the version used, whether HTTP Keep-Alive is enabled, etc...', 'This test is informational only and does not denote any security problem.']</t>
@@ -13191,7 +11507,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>{"plugin_id": 24260, "publication_date": "2007/01/30", "modification_date": "2024/02/26"}</t>
+          <t>{"publication_date": "2007/01/30", "modification_date": "2024/02/26", "family": null, "severity": null, "plugin_id": 24260}</t>
         </is>
       </c>
     </row>
@@ -13211,16 +11527,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13244,11 +11552,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -13264,7 +11568,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -13284,16 +11588,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13317,11 +11613,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -13337,7 +11629,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -13357,16 +11649,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13390,11 +11674,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -13410,7 +11690,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -13430,16 +11710,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13463,11 +11735,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -13483,7 +11751,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -13503,16 +11771,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13536,11 +11796,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -13556,7 +11812,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -13576,16 +11832,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13609,11 +11857,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -13629,7 +11873,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -13649,16 +11893,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13682,11 +11918,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -13702,7 +11934,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -13722,11 +11954,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -13755,27 +11983,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
         <v>25220</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -13795,16 +12015,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -13828,11 +12040,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -13848,7 +12056,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -13868,11 +12076,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -13921,7 +12125,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -13941,11 +12145,7 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>['https://www.itu.int/rec/T-REC-X.509/en', 'https://en.wikipedia.org/wiki/X.509']</t>
@@ -13994,7 +12194,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>{"plugin_id": 51192, "publication_date": "2010/12/15", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2010/12/15", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 51192}</t>
         </is>
       </c>
     </row>
@@ -14014,11 +12214,7 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>['https://www.itu.int/rec/T-REC-X.509/en', 'https://en.wikipedia.org/wiki/X.509']</t>
@@ -14067,7 +12263,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>{"plugin_id": 51192, "publication_date": "2010/12/15", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2010/12/15", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 51192}</t>
         </is>
       </c>
     </row>
@@ -14087,16 +12283,8 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -14140,7 +12328,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57582, "publication_date": "2012/01/17", "modification_date": "2022/06/14"}</t>
+          <t>{"publication_date": "2012/01/17", "modification_date": "2022/06/14", "family": null, "severity": null, "plugin_id": 57582}</t>
         </is>
       </c>
     </row>
@@ -14160,16 +12348,8 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -14213,7 +12393,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57582, "publication_date": "2012/01/17", "modification_date": "2022/06/14"}</t>
+          <t>{"publication_date": "2012/01/17", "modification_date": "2022/06/14", "family": null, "severity": null, "plugin_id": 57582}</t>
         </is>
       </c>
     </row>
@@ -14233,11 +12413,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -14286,7 +12462,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -14306,11 +12482,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -14339,11 +12511,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -14359,7 +12527,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -14379,16 +12547,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14412,11 +12572,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -14432,7 +12588,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -14452,16 +12608,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14485,11 +12633,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -14505,7 +12649,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -14525,11 +12669,7 @@
           <t>['Configure the remote web server to use HSTS.']</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc6797']</t>
@@ -14558,11 +12698,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>['The remote HTTPS server is not enforcing HTTP Strict Transport Security (HSTS). HSTS is an optional response header that can be configured on the server to instruct the browser to only communicate via HTTPS. The lack of HSTS allows downgrade attacks, SSL-stripping man-in-the-middle attacks, and weakens cookie-hijacking protections.']</t>
@@ -14578,7 +12714,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{"plugin_id": 84502, "publication_date": "2015/07/02", "modification_date": "2024/08/09"}</t>
+          <t>{"publication_date": "2015/07/02", "modification_date": "2024/08/09", "family": null, "severity": null, "plugin_id": 84502}</t>
         </is>
       </c>
     </row>
@@ -14598,11 +12734,7 @@
           <t>['Configure the remote web server to use HSTS.']</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc6797']</t>
@@ -14631,11 +12763,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>['The remote HTTPS server is not enforcing HTTP Strict Transport Security (HSTS). HSTS is an optional response header that can be configured on the server to instruct the browser to only communicate via HTTPS. The lack of HSTS allows downgrade attacks, SSL-stripping man-in-the-middle attacks, and weakens cookie-hijacking protections.']</t>
@@ -14651,7 +12779,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{"plugin_id": 84502, "publication_date": "2015/07/02", "modification_date": "2024/08/09"}</t>
+          <t>{"publication_date": "2015/07/02", "modification_date": "2024/08/09", "family": null, "severity": null, "plugin_id": 84502}</t>
         </is>
       </c>
     </row>
@@ -14671,11 +12799,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?d9c03a9a', 'http://www.nessus.org/u?b019cbdb', 'https://www.owasp.org/index.php/Test_HTTP_Methods_(OTG-CONFIG-006)']</t>
@@ -14704,11 +12828,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>['By calling the OPTIONS method, it is possible to determine which HTTP methods are allowed on each directory.', 'The following HTTP methods are considered insecure:\n  PUT, DELETE, CONNECT, TRACE, HEAD', "Many frameworks and languages treat 'HEAD' as a 'GET' request, albeit one without any body in the response. If a security constraint was set on 'GET' requests such that only 'authenticatedUsers' could access GET requests for a particular servlet or resource, it would be bypassed for the 'HEAD' version. This allowed unauthorized blind submission of any privileged GET request.", "As this list may be incomplete, the plugin also tests - if 'Thorough tests' are enabled or 'Enable web applications tests' is set to 'yes'\nin the scan policy - various known HTTP methods on each directory and considers them as unsupported if it receives a response code of 400, 403, 405, or 501.", 'Note that the plugin output is only informational and does not necessarily indicate the presence of any security vulnerabilities.']</t>
@@ -14724,7 +12844,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{"plugin_id": 43111, "publication_date": "2009/12/10", "modification_date": "2022/04/11"}</t>
+          <t>{"publication_date": "2009/12/10", "modification_date": "2022/04/11", "family": null, "severity": null, "plugin_id": 43111}</t>
         </is>
       </c>
     </row>
@@ -14744,16 +12864,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14777,11 +12889,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -14797,7 +12905,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -14817,16 +12925,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14850,11 +12950,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>['This test gives some information about the remote HTTP protocol - the version used, whether HTTP Keep-Alive is enabled, etc...', 'This test is informational only and does not denote any security problem.']</t>
@@ -14870,7 +12966,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{"plugin_id": 24260, "publication_date": "2007/01/30", "modification_date": "2024/02/26"}</t>
+          <t>{"publication_date": "2007/01/30", "modification_date": "2024/02/26", "family": null, "severity": null, "plugin_id": 24260}</t>
         </is>
       </c>
     </row>
@@ -14890,16 +12986,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14923,11 +13011,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>['This test gives some information about the remote HTTP protocol - the version used, whether HTTP Keep-Alive is enabled, etc...', 'This test is informational only and does not denote any security problem.']</t>
@@ -14943,7 +13027,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{"plugin_id": 24260, "publication_date": "2007/01/30", "modification_date": "2024/02/26"}</t>
+          <t>{"publication_date": "2007/01/30", "modification_date": "2024/02/26", "family": null, "severity": null, "plugin_id": 24260}</t>
         </is>
       </c>
     </row>
@@ -14963,16 +13047,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -14996,11 +13072,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -15016,7 +13088,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -15036,16 +13108,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15069,11 +13133,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -15089,7 +13149,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -15109,16 +13169,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15142,11 +13194,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -15162,7 +13210,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -15182,16 +13230,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15215,11 +13255,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -15235,7 +13271,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -15255,16 +13291,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15288,11 +13316,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -15308,7 +13332,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -15328,11 +13352,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?7a390f87', 'http://www.nessus.org/u?ad7d6b3b', 'http://www.nessus.org/u?1c0c61e0', 'http://www.nessus.org/u?5eec4b28']</t>
@@ -15361,11 +13381,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>['This plugin reports network services that offer post-quantum ciphers and enumerates the post-quantum ciphers that they offer.  Tenable makes no attempt to determine whether the remote service is actually hardened against a post-quantum attack.']</t>
@@ -15381,7 +13397,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277653, "publication_date": "2025/12/08", "modification_date": "2025/12/08"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2025/12/08", "family": null, "severity": null, "plugin_id": 277653}</t>
         </is>
       </c>
     </row>
@@ -15401,11 +13417,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?7a390f87', 'http://www.nessus.org/u?ad7d6b3b', 'http://www.nessus.org/u?1c0c61e0', 'http://www.nessus.org/u?5eec4b28']</t>
@@ -15434,11 +13446,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>['This plugin reports network services that offer post-quantum ciphers and enumerates the post-quantum ciphers that they offer.  Tenable makes no attempt to determine whether the remote service is actually hardened against a post-quantum attack.']</t>
@@ -15454,7 +13462,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277653, "publication_date": "2025/12/08", "modification_date": "2025/12/08"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2025/12/08", "family": null, "severity": null, "plugin_id": 277653}</t>
         </is>
       </c>
     </row>
@@ -15474,16 +13482,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15507,11 +13507,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL and TLS versions are supported by the remote service for encrypting communications.']</t>
@@ -15527,7 +13523,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{"plugin_id": 56984, "publication_date": "2011/12/01", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2011/12/01", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 56984}</t>
         </is>
       </c>
     </row>
@@ -15547,16 +13543,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15580,11 +13568,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL and TLS versions are supported by the remote service for encrypting communications.']</t>
@@ -15600,7 +13584,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{"plugin_id": 56984, "publication_date": "2011/12/01", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2011/12/01", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 56984}</t>
         </is>
       </c>
     </row>
@@ -15620,16 +13604,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15653,11 +13629,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>['This plugin connects to every SSL-related port and attempts to extract and dump the X.509 certificate.']</t>
@@ -15673,7 +13645,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10863, "publication_date": "2008/05/19", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2008/05/19", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 10863}</t>
         </is>
       </c>
     </row>
@@ -15693,16 +13665,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -15726,11 +13690,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>['This plugin connects to every SSL-related port and attempts to extract and dump the X.509 certificate.']</t>
@@ -15746,7 +13706,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10863, "publication_date": "2008/05/19", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2008/05/19", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 10863}</t>
         </is>
       </c>
     </row>
@@ -15766,11 +13726,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'http://www.nessus.org/u?cc4a822a', 'https://www.openssl.org/~bodo/tls-cbc.txt']</t>
@@ -15799,11 +13755,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>['The remote host supports the use of SSL ciphers that operate in Cipher Block Chaining (CBC) mode.  These cipher suites offer additional security over Electronic Codebook (ECB) mode, but have the potential to leak information if used improperly.']</t>
@@ -15819,7 +13771,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{"plugin_id": 70544, "publication_date": "2013/10/22", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2013/10/22", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 70544}</t>
         </is>
       </c>
     </row>
@@ -15839,11 +13791,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'http://www.nessus.org/u?cc4a822a', 'https://www.openssl.org/~bodo/tls-cbc.txt']</t>
@@ -15872,11 +13820,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>['The remote host supports the use of SSL ciphers that operate in Cipher Block Chaining (CBC) mode.  These cipher suites offer additional security over Electronic Codebook (ECB) mode, but have the potential to leak information if used improperly.']</t>
@@ -15892,7 +13836,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{"plugin_id": 70544, "publication_date": "2013/10/22", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2013/10/22", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 70544}</t>
         </is>
       </c>
     </row>
@@ -15912,11 +13856,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/man1.0.2/man1/ciphers.html', 'http://www.nessus.org/u?e17ffced']</t>
@@ -15945,11 +13885,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL ciphers are supported by the remote service for encrypting communications.']</t>
@@ -15965,7 +13901,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{"plugin_id": 21643, "publication_date": "2006/06/05", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2006/06/05", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 21643}</t>
         </is>
       </c>
     </row>
@@ -15985,11 +13921,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/man1.0.2/man1/ciphers.html', 'http://www.nessus.org/u?e17ffced']</t>
@@ -16018,11 +13950,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL ciphers are supported by the remote service for encrypting communications.']</t>
@@ -16038,7 +13966,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{"plugin_id": 21643, "publication_date": "2006/06/05", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2006/06/05", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 21643}</t>
         </is>
       </c>
     </row>
@@ -16058,11 +13986,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'https://en.wikipedia.org/wiki/Diffie-Hellman_key_exchange', 'https://en.wikipedia.org/wiki/Perfect_forward_secrecy']</t>
@@ -16091,11 +14015,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>["The remote host supports the use of SSL ciphers that offer Perfect Forward Secrecy (PFS) encryption.  These cipher suites ensure that recorded SSL traffic cannot be broken at a future date if the server's private key is compromised."]</t>
@@ -16111,7 +14031,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57041, "publication_date": "2011/12/07", "modification_date": "2021/03/09"}</t>
+          <t>{"publication_date": "2011/12/07", "modification_date": "2021/03/09", "family": null, "severity": null, "plugin_id": 57041}</t>
         </is>
       </c>
     </row>
@@ -16131,11 +14051,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'https://en.wikipedia.org/wiki/Diffie-Hellman_key_exchange', 'https://en.wikipedia.org/wiki/Perfect_forward_secrecy']</t>
@@ -16164,11 +14080,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>["The remote host supports the use of SSL ciphers that offer Perfect Forward Secrecy (PFS) encryption.  These cipher suites ensure that recorded SSL traffic cannot be broken at a future date if the server's private key is compromised."]</t>
@@ -16184,7 +14096,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57041, "publication_date": "2011/12/07", "modification_date": "2021/03/09"}</t>
+          <t>{"publication_date": "2011/12/07", "modification_date": "2021/03/09", "family": null, "severity": null, "plugin_id": 57041}</t>
         </is>
       </c>
     </row>
@@ -16204,11 +14116,7 @@
           <t>['Only enable support for recommened cipher suites.']</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>['https://wiki.mozilla.org/Security/Server_Side_TLS', 'https://ssl-config.mozilla.org/']</t>
@@ -16237,11 +14145,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
           <t>['The remote host has open SSL/TLS ports which advertise discouraged cipher suites. It is recommended to only enable support for the following cipher suites:', 'TLSv1.3:\n  - 0x13,0x01 TLS13_AES_128_GCM_SHA256\n  - 0x13,0x02 TLS13_AES_256_GCM_SHA384\n  - 0x13,0x03 TLS13_CHACHA20_POLY1305_SHA256', 'TLSv1.2:\n  - 0xC0,0x2B ECDHE-ECDSA-AES128-GCM-SHA256\n  - 0xC0,0x2F ECDHE-RSA-AES128-GCM-SHA256\n  - 0xC0,0x2C ECDHE-ECDSA-AES256-GCM-SHA384\n  - 0xC0,0x30 ECDHE-RSA-AES256-GCM-SHA384\n  - 0xCC,0xA9 ECDHE-ECDSA-CHACHA20-POLY1305\n  - 0xCC,0xA8 ECDHE-RSA-CHACHA20-POLY1305', 'This is the recommended configuration for the vast majority of services, as it is highly secure and compatible with nearly every client released in the last five (or more) years.']</t>
@@ -16257,7 +14161,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{"plugin_id": 156899, "publication_date": "2022/01/20", "modification_date": "2024/02/12"}</t>
+          <t>{"publication_date": "2022/01/20", "modification_date": "2024/02/12", "family": null, "severity": null, "plugin_id": 156899}</t>
         </is>
       </c>
     </row>
@@ -16277,11 +14181,7 @@
           <t>['Only enable support for recommened cipher suites.']</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>['https://wiki.mozilla.org/Security/Server_Side_TLS', 'https://ssl-config.mozilla.org/']</t>
@@ -16310,11 +14210,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>['The remote host has open SSL/TLS ports which advertise discouraged cipher suites. It is recommended to only enable support for the following cipher suites:', 'TLSv1.3:\n  - 0x13,0x01 TLS13_AES_128_GCM_SHA256\n  - 0x13,0x02 TLS13_AES_256_GCM_SHA384\n  - 0x13,0x03 TLS13_CHACHA20_POLY1305_SHA256', 'TLSv1.2:\n  - 0xC0,0x2B ECDHE-ECDSA-AES128-GCM-SHA256\n  - 0xC0,0x2F ECDHE-RSA-AES128-GCM-SHA256\n  - 0xC0,0x2C ECDHE-ECDSA-AES256-GCM-SHA384\n  - 0xC0,0x30 ECDHE-RSA-AES256-GCM-SHA384\n  - 0xCC,0xA9 ECDHE-ECDSA-CHACHA20-POLY1305\n  - 0xCC,0xA8 ECDHE-RSA-CHACHA20-POLY1305', 'This is the recommended configuration for the vast majority of services, as it is highly secure and compatible with nearly every client released in the last five (or more) years.']</t>
@@ -16330,7 +14226,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{"plugin_id": 156899, "publication_date": "2022/01/20", "modification_date": "2024/02/12"}</t>
+          <t>{"publication_date": "2022/01/20", "modification_date": "2024/02/12", "family": null, "severity": null, "plugin_id": 156899}</t>
         </is>
       </c>
     </row>
@@ -16350,16 +14246,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -16383,11 +14271,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -16403,7 +14287,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -16423,16 +14307,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -16456,11 +14332,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -16476,7 +14348,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -16496,11 +14368,7 @@
           <t>['Replace affected ciphers with algorithms chosen to resist CRQC attack.']</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?54fba2c1']</t>
@@ -16529,11 +14397,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
           <t>["This plugin reports network services that may be vulnerable now to a future attack by adversaries using a cryptographically relevant quantum computer (CRQC). Shor's is a theoretical algorithm that leverages the unique ability of quantum computation to do massively parallel calculations developed by Peter Shor in 1994.", "This algorithm easily computes two classically difficult mathematical problems used in modern cryptography; discrete logarithms, and factoring numbers formed by multiplying large primes.  Shor's reduces both of these problems from taking exponential time in chosen cases to being solvable in polynomial time.", "Asymmetric encryption algorithms such as RSA, Diffie-Hellman and Elliptic Curve Diffie-Hellman are impacted by Shor's Algorithm.  The most common uses of these algorithms are in symmetric key establishment and authentication.  These uses render Shor's Algorithm particularly dangerous because it may give an adversary the ability to harvest network communications now, and in the future, when a CRQC becomes available, extract the symmetric key and decrypt the communication."]</t>
@@ -16549,7 +14413,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{"plugin_id": 298387, "publication_date": "2026/02/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2026/02/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 298387}</t>
         </is>
       </c>
     </row>
@@ -16569,11 +14433,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -16602,27 +14462,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="N222" t="n">
         <v>25220</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -16642,11 +14494,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc7301']</t>
@@ -16675,11 +14523,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
           <t>['The remote host supports the TLS ALPN extension. This plugin enumerates the protocols the extension supports.']</t>
@@ -16695,7 +14539,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{"plugin_id": 84821, "publication_date": "2015/07/17", "modification_date": "2024/09/11"}</t>
+          <t>{"publication_date": "2015/07/17", "modification_date": "2024/09/11", "family": null, "severity": null, "plugin_id": 84821}</t>
         </is>
       </c>
     </row>
@@ -16715,16 +14559,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -16748,11 +14584,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>['This plugin detects which TLS supported groups entries are supported by the remote service.']</t>
@@ -16768,7 +14600,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277654, "publication_date": "2025/12/08", "modification_date": "2026/06/15"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2026/06/15", "family": null, "severity": null, "plugin_id": 277654}</t>
         </is>
       </c>
     </row>
@@ -16788,16 +14620,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -16821,11 +14645,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>['This plugin detects which TLS supported groups entries are supported by the remote service.']</t>
@@ -16841,7 +14661,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277654, "publication_date": "2025/12/08", "modification_date": "2026/06/15"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2026/06/15", "family": null, "severity": null, "plugin_id": 277654}</t>
         </is>
       </c>
     </row>
@@ -16861,11 +14681,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc5246']</t>
@@ -16894,11 +14710,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.2.']</t>
@@ -16914,7 +14726,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{"plugin_id": 136318, "publication_date": "2020/05/04", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/05/04", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 136318}</t>
         </is>
       </c>
     </row>
@@ -16934,11 +14746,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc5246']</t>
@@ -16967,11 +14775,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.2.']</t>
@@ -16987,7 +14791,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{"plugin_id": 136318, "publication_date": "2020/05/04", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/05/04", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 136318}</t>
         </is>
       </c>
     </row>
@@ -17007,11 +14811,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc8446']</t>
@@ -17040,11 +14840,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.3.']</t>
@@ -17060,7 +14856,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{"plugin_id": 138330, "publication_date": "2020/07/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/07/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 138330}</t>
         </is>
       </c>
     </row>
@@ -17080,11 +14876,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc8446']</t>
@@ -17113,11 +14905,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.3.']</t>
@@ -17133,7 +14921,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{"plugin_id": 138330, "publication_date": "2020/07/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/07/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 138330}</t>
         </is>
       </c>
     </row>
@@ -17153,16 +14941,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -17186,11 +14966,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -17206,7 +14982,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -17226,11 +15002,7 @@
           <t>['Contact the vendor of the DNS software for a fix.']</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>['http://cs.unc.edu/~fabian/course_papers/cache_snooping.pdf']</t>
@@ -17279,7 +15051,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12217, "publication_date": "2004/04/27", "modification_date": "2020/04/07"}</t>
+          <t>{"publication_date": "2004/04/27", "modification_date": "2020/04/07", "family": null, "severity": null, "plugin_id": 12217}</t>
         </is>
       </c>
     </row>
@@ -17299,11 +15071,7 @@
           <t>['On Linux, you can disable IP forwarding by doing :', 'echo 0 &gt; /proc/sys/net/ipv4/ip_forward', "On Windows, set the key 'IPEnableRouter' to 0 under", 'HKEY_LOCAL_MACHINE\\System\\CurrentControlSet\\Services\\Tcpip\\Parameters', 'On Mac OS X, you can disable IP forwarding by executing the command :', 'sysctl -w net.inet.ip.forwarding=0', 'For other systems, check with your vendor.']</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0511']</t>
@@ -17352,7 +15120,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{"plugin_id": 50686, "publication_date": "2010/11/23", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2010/11/23", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 50686}</t>
         </is>
       </c>
     </row>
@@ -17372,11 +15140,7 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>['https://www.itu.int/rec/T-REC-X.509/en', 'https://en.wikipedia.org/wiki/X.509']</t>
@@ -17425,7 +15189,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{"plugin_id": 51192, "publication_date": "2010/12/15", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2010/12/15", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 51192}</t>
         </is>
       </c>
     </row>
@@ -17445,16 +15209,8 @@
           <t>['Purchase or generate a new SSL certificate to replace the existing one.']</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -17498,7 +15254,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{"plugin_id": 15901, "publication_date": "2004/12/03", "modification_date": "2025/12/08"}</t>
+          <t>{"publication_date": "2004/12/03", "modification_date": "2025/12/08", "family": null, "severity": null, "plugin_id": 15901}</t>
         </is>
       </c>
     </row>
@@ -17518,16 +15274,8 @@
           <t>['Purchase or generate a proper SSL certificate for this service.']</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -17571,7 +15319,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57582, "publication_date": "2012/01/17", "modification_date": "2022/06/14"}</t>
+          <t>{"publication_date": "2012/01/17", "modification_date": "2022/06/14", "family": null, "severity": null, "plugin_id": 57582}</t>
         </is>
       </c>
     </row>
@@ -17591,11 +15339,7 @@
           <t>['Filter out the ICMP timestamp requests (13), and the outgoing ICMP timestamp replies (14).']</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>['CVE CVE-1999-0524', 'XREF CWE:200']</t>
@@ -17644,7 +15388,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10114, "publication_date": "1999/08/01", "modification_date": "2024/10/07"}</t>
+          <t>{"publication_date": "1999/08/01", "modification_date": "2024/10/07", "family": null, "severity": null, "plugin_id": 10114}</t>
         </is>
       </c>
     </row>
@@ -17664,11 +15408,7 @@
           <t>['If you want to test them, re-scan using the special vhost syntax, such as :', 'www.example.com[192.0.32.10]']</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>['https://en.wikipedia.org/wiki/Virtual_hosting']</t>
@@ -17697,11 +15437,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>['Hostnames different from the current hostname have been collected by miscellaneous plugins. Nessus has generated a list of hostnames that point to the remote host. Note that these are only the alternate hostnames for vhosts discovered on a web server.', 'Different web servers may be hosted on name-based virtual hosts.']</t>
@@ -17717,7 +15453,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{"plugin_id": 46180, "publication_date": "2010/04/29", "modification_date": "2022/08/15"}</t>
+          <t>{"publication_date": "2010/04/29", "modification_date": "2022/08/15", "family": null, "severity": null, "plugin_id": 46180}</t>
         </is>
       </c>
     </row>
@@ -17737,11 +15473,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>['http://cpe.mitre.org/', 'https://nvd.nist.gov/products/cpe']</t>
@@ -17770,11 +15502,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
           <t>['By using information obtained from a Nessus scan, this plugin reports CPE (Common Platform Enumeration) matches for various hardware and software products found on a host.', 'Note that if an official CPE is not available for the product, this plugin computes the best possible CPE based on the information available from the scan.']</t>
@@ -17790,7 +15518,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{"plugin_id": 45590, "publication_date": "2010/04/21", "modification_date": "2026/06/16"}</t>
+          <t>{"publication_date": "2010/04/21", "modification_date": "2026/06/16", "family": null, "severity": null, "plugin_id": 45590}</t>
         </is>
       </c>
     </row>
@@ -17810,11 +15538,7 @@
           <t>["It is possible to hide the version number of BIND by using the 'version' directive in the 'options' section in named.conf."]</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0583']</t>
@@ -17843,11 +15567,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
           <t>["The remote host is running BIND or another DNS server that reports its version number when it receives a special request for the text 'version.bind' in the domain 'chaos'.", 'This version is not necessarily accurate and could even be forged, as some DNS servers send the information based on a configuration file.']</t>
@@ -17863,7 +15583,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10028, "publication_date": "1999/10/12", "modification_date": "2022/10/12"}</t>
+          <t>{"publication_date": "1999/10/12", "modification_date": "2022/10/12", "family": null, "severity": null, "plugin_id": 10028}</t>
         </is>
       </c>
     </row>
@@ -17883,11 +15603,7 @@
           <t>['Disable this service if it is not needed or restrict access to internal hosts only if the service is available externally.']</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>['https://en.wikipedia.org/wiki/Domain_Name_System']</t>
@@ -17916,27 +15632,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>['The remote service is a Domain Name System (DNS) server, which provides a mapping between hostnames and IP addresses.']</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M240" t="inlineStr"/>
       <c r="N240" t="n">
         <v>11002</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11002, "publication_date": "2003/02/13", "modification_date": "2017/05/16"}</t>
+          <t>{"publication_date": "2003/02/13", "modification_date": "2017/05/16", "family": null, "severity": null, "plugin_id": 11002}</t>
         </is>
       </c>
     </row>
@@ -17956,11 +15664,7 @@
           <t>['Disable this service if it is not needed or restrict access to internal hosts only if the service is available externally.']</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>['https://en.wikipedia.org/wiki/Domain_Name_System']</t>
@@ -17989,27 +15693,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>['The remote service is a Domain Name System (DNS) server, which provides a mapping between hostnames and IP addresses.']</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
         <v>11002</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11002, "publication_date": "2003/02/13", "modification_date": "2017/05/16"}</t>
+          <t>{"publication_date": "2003/02/13", "modification_date": "2017/05/16", "family": null, "severity": null, "plugin_id": 11002}</t>
         </is>
       </c>
     </row>
@@ -18029,11 +15725,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0030', 'XREF IAVT:0001-T-0937']</t>
@@ -18062,11 +15754,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>['Nessus was able to obtain version information by sending a special TXT record query to the remote host.', 'Note that this version is not necessarily accurate and could even be forged, as some DNS servers send the information based on a configuration file.']</t>
@@ -18082,7 +15770,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{"plugin_id": 72779, "publication_date": "2014/03/03", "modification_date": "2024/09/24"}</t>
+          <t>{"publication_date": "2014/03/03", "modification_date": "2024/09/24", "family": null, "severity": null, "plugin_id": 72779}</t>
         </is>
       </c>
     </row>
@@ -18102,16 +15790,8 @@
           <t>["It may be possible to disable this feature.  Consult the vendor's documentation for more information."]</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18135,11 +15815,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>["It is possible to learn the remote host name by querying the remote DNS server for 'hostname.bind' in the CHAOS domain."]</t>
@@ -18155,7 +15831,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{"plugin_id": 35371, "publication_date": "2009/01/15", "modification_date": "2011/09/14"}</t>
+          <t>{"publication_date": "2009/01/15", "modification_date": "2011/09/14", "family": null, "severity": null, "plugin_id": 35371}</t>
         </is>
       </c>
     </row>
@@ -18175,16 +15851,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18208,11 +15876,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>['Based on the remote operating system, it is possible to determine what the remote system type is (eg: a printer, router, general-purpose computer, etc).']</t>
@@ -18228,7 +15892,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{"plugin_id": 54615, "publication_date": "2011/05/23", "modification_date": "2025/03/12"}</t>
+          <t>{"publication_date": "2011/05/23", "modification_date": "2025/03/12", "family": null, "severity": null, "plugin_id": 54615}</t>
         </is>
       </c>
     </row>
@@ -18248,16 +15912,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18281,27 +15937,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>['The remote web server cannot host user-supplied CGIs. CGI scanning will be disabled on this server.']</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="n">
         <v>19689</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19689, "publication_date": "2005/09/14", "modification_date": "2025/09/29"}</t>
+          <t>{"publication_date": "2005/09/14", "modification_date": "2025/09/29", "family": null, "severity": null, "plugin_id": 19689}</t>
         </is>
       </c>
     </row>
@@ -18321,16 +15969,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18354,11 +15994,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>['This plugin gathers MAC addresses discovered from both remote probing of the host (e.g. SNMP and Netbios) and from running local checks (e.g. ifconfig). It then consolidates the MAC addresses into a single, unique, and uniform list.']</t>
@@ -18374,7 +16010,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{"plugin_id": 86420, "publication_date": "2015/10/16", "modification_date": "2025/06/10"}</t>
+          <t>{"publication_date": "2015/10/16", "modification_date": "2025/06/10", "family": null, "severity": null, "plugin_id": 86420}</t>
         </is>
       </c>
     </row>
@@ -18394,11 +16030,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>['XREF IAVT:0001-T-0931']</t>
@@ -18427,11 +16059,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>['This plugin attempts to determine the type and the version of the   remote web server.']</t>
@@ -18447,7 +16075,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10107, "publication_date": "2000/01/04", "modification_date": "2020/10/30"}</t>
+          <t>{"publication_date": "2000/01/04", "modification_date": "2020/10/30", "family": null, "severity": null, "plugin_id": 10107}</t>
         </is>
       </c>
     </row>
@@ -18467,16 +16095,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18500,11 +16120,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>['Nessus was able to resolve the fully qualified domain name (FQDN) of the remote host.']</t>
@@ -18520,7 +16136,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{"plugin_id": 12053, "publication_date": "2004/02/11", "modification_date": "2025/03/13"}</t>
+          <t>{"publication_date": "2004/02/11", "modification_date": "2025/03/13", "family": null, "severity": null, "plugin_id": 12053}</t>
         </is>
       </c>
     </row>
@@ -18540,16 +16156,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18573,11 +16181,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -18593,7 +16197,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -18613,16 +16217,8 @@
           <t>['Protect your target with an IP filter.']</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18646,11 +16242,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>["This plugin is a SYN 'half-open' port scanner.  It shall be reasonably quick even against a firewalled target.", 'Note that SYN scans are less intrusive than TCP (full connect) scans against broken services, but they might cause problems for less robust firewalls and also leave unclosed connections on the remote target, if the network is loaded.']</t>
@@ -18666,7 +16258,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11219, "publication_date": "2009/02/04", "modification_date": "2025/07/14"}</t>
+          <t>{"publication_date": "2009/02/04", "modification_date": "2025/07/14", "family": null, "severity": null, "plugin_id": 11219}</t>
         </is>
       </c>
     </row>
@@ -18686,16 +16278,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18719,11 +16303,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
           <t>['This plugin displays, for each tested host, information about the scan itself :', '- The version of the plugin set.\n  - The type of scanner (Nessus or Nessus Home).\n  - The version of the Nessus Engine.\n  - The port scanner(s) used.\n  - The port range scanned.\n  - The ping round trip time \n  - Whether credentialed or third-party patch management     checks are possible.\n  - Whether the display of superseded patches is enabled\n  - The date of the scan.\n  - The duration of the scan.\n  - The number of hosts scanned in parallel.\n  - The number of checks done in parallel.']</t>
@@ -18739,7 +16319,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{"plugin_id": 19506, "publication_date": "2005/08/26", "modification_date": "2026/07/10"}</t>
+          <t>{"publication_date": "2005/08/26", "modification_date": "2026/07/10", "family": null, "severity": null, "plugin_id": 19506}</t>
         </is>
       </c>
     </row>
@@ -18759,16 +16339,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18792,11 +16364,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (TCP/IP, SMB, HTTP, NTP, SNMP, etc), it was possible to gather one or more fingerprints from the remote system. While the highest-confidence result was reported in plugin 11936, “OS Identification”, the complete set of fingerprints detected are reported here.']</t>
@@ -18812,7 +16380,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>{"plugin_id": 209654, "publication_date": "2025/02/26", "modification_date": "2025/03/03"}</t>
+          <t>{"publication_date": "2025/02/26", "modification_date": "2025/03/03", "family": null, "severity": null, "plugin_id": 209654}</t>
         </is>
       </c>
     </row>
@@ -18832,16 +16400,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -18865,11 +16425,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>['Using a combination of remote probes (e.g., TCP/IP, SMB, HTTP, NTP, SNMP, etc.), it is possible to guess the name of the remote operating system in use. It is also possible sometimes to guess the version of the operating system.']</t>
@@ -18885,7 +16441,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{"plugin_id": 11936, "publication_date": "2003/12/09", "modification_date": "2025/06/03"}</t>
+          <t>{"publication_date": "2003/12/09", "modification_date": "2025/06/03", "family": null, "severity": null, "plugin_id": 11936}</t>
         </is>
       </c>
     </row>
@@ -18905,11 +16461,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?7a390f87', 'http://www.nessus.org/u?ad7d6b3b', 'http://www.nessus.org/u?1c0c61e0', 'http://www.nessus.org/u?5eec4b28']</t>
@@ -18938,11 +16490,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>['This plugin reports network services that do not offer post-quantum ciphers.  Tenable makes no attempt to determine whether the remote service would be vulnerable to a post-quantum attack.', "However, cryptography that depends on the classic difficulty of solving the discrete logarithm problem or on the classic difficulty of large prime factorization is broken by Shor's algorithm.  Examples of this are RSA asymmetric encryption and Diffie-Hellman key exchange."]</t>
@@ -18958,7 +16506,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277650, "publication_date": "2025/12/08", "modification_date": "2025/12/08"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2025/12/08", "family": null, "severity": null, "plugin_id": 277650}</t>
         </is>
       </c>
     </row>
@@ -18978,16 +16526,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -19011,11 +16551,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL and TLS versions are supported by the remote service for encrypting communications.']</t>
@@ -19031,7 +16567,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{"plugin_id": 56984, "publication_date": "2011/12/01", "modification_date": "2025/06/16"}</t>
+          <t>{"publication_date": "2011/12/01", "modification_date": "2025/06/16", "family": null, "severity": null, "plugin_id": 56984}</t>
         </is>
       </c>
     </row>
@@ -19051,16 +16587,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -19084,11 +16612,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>['This plugin connects to every SSL-related port and attempts to extract and dump the X.509 certificate.']</t>
@@ -19104,7 +16628,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10863, "publication_date": "2008/05/19", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2008/05/19", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 10863}</t>
         </is>
       </c>
     </row>
@@ -19124,11 +16648,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'http://www.nessus.org/u?cc4a822a', 'https://www.openssl.org/~bodo/tls-cbc.txt']</t>
@@ -19157,11 +16677,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>['The remote host supports the use of SSL ciphers that operate in Cipher Block Chaining (CBC) mode.  These cipher suites offer additional security over Electronic Codebook (ECB) mode, but have the potential to leak information if used improperly.']</t>
@@ -19177,7 +16693,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{"plugin_id": 70544, "publication_date": "2013/10/22", "modification_date": "2021/02/03"}</t>
+          <t>{"publication_date": "2013/10/22", "modification_date": "2021/02/03", "family": null, "severity": null, "plugin_id": 70544}</t>
         </is>
       </c>
     </row>
@@ -19197,11 +16713,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/man1.0.2/man1/ciphers.html', 'http://www.nessus.org/u?e17ffced']</t>
@@ -19230,11 +16742,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>['This plugin detects which SSL ciphers are supported by the remote service for encrypting communications.']</t>
@@ -19250,7 +16758,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{"plugin_id": 21643, "publication_date": "2006/06/05", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2006/06/05", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 21643}</t>
         </is>
       </c>
     </row>
@@ -19270,11 +16778,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>['https://www.openssl.org/docs/manmaster/man1/ciphers.html', 'https://en.wikipedia.org/wiki/Diffie-Hellman_key_exchange', 'https://en.wikipedia.org/wiki/Perfect_forward_secrecy']</t>
@@ -19303,11 +16807,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>["The remote host supports the use of SSL ciphers that offer Perfect Forward Secrecy (PFS) encryption.  These cipher suites ensure that recorded SSL traffic cannot be broken at a future date if the server's private key is compromised."]</t>
@@ -19323,7 +16823,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{"plugin_id": 57041, "publication_date": "2011/12/07", "modification_date": "2021/03/09"}</t>
+          <t>{"publication_date": "2011/12/07", "modification_date": "2021/03/09", "family": null, "severity": null, "plugin_id": 57041}</t>
         </is>
       </c>
     </row>
@@ -19343,11 +16843,7 @@
           <t>["Ensure that use of this root Certification Authority certificate complies with your organization's acceptable use and security policies."]</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>['https://docs.microsoft.com/en-us/previous-versions/windows/it-pro/windows-server-2003/cc778623(v=ws.10)']</t>
@@ -19376,11 +16872,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>['The remote service uses an SSL certificate chain that contains a self-signed root Certification Authority certificate at the top of the chain.']</t>
@@ -19396,7 +16888,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{"plugin_id": 94761, "publication_date": "2016/11/14", "modification_date": "2018/11/15"}</t>
+          <t>{"publication_date": "2016/11/14", "modification_date": "2018/11/15", "family": null, "severity": null, "plugin_id": 94761}</t>
         </is>
       </c>
     </row>
@@ -19416,11 +16908,7 @@
           <t>['Only enable support for recommened cipher suites.']</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>['https://wiki.mozilla.org/Security/Server_Side_TLS', 'https://ssl-config.mozilla.org/']</t>
@@ -19449,11 +16937,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>['The remote host has open SSL/TLS ports which advertise discouraged cipher suites. It is recommended to only enable support for the following cipher suites:', 'TLSv1.3:\n  - 0x13,0x01 TLS13_AES_128_GCM_SHA256\n  - 0x13,0x02 TLS13_AES_256_GCM_SHA384\n  - 0x13,0x03 TLS13_CHACHA20_POLY1305_SHA256', 'TLSv1.2:\n  - 0xC0,0x2B ECDHE-ECDSA-AES128-GCM-SHA256\n  - 0xC0,0x2F ECDHE-RSA-AES128-GCM-SHA256\n  - 0xC0,0x2C ECDHE-ECDSA-AES256-GCM-SHA384\n  - 0xC0,0x30 ECDHE-RSA-AES256-GCM-SHA384\n  - 0xCC,0xA9 ECDHE-ECDSA-CHACHA20-POLY1305\n  - 0xCC,0xA8 ECDHE-RSA-CHACHA20-POLY1305', 'This is the recommended configuration for the vast majority of services, as it is highly secure and compatible with nearly every client released in the last five (or more) years.']</t>
@@ -19469,7 +16953,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{"plugin_id": 156899, "publication_date": "2022/01/20", "modification_date": "2024/02/12"}</t>
+          <t>{"publication_date": "2022/01/20", "modification_date": "2024/02/12", "family": null, "severity": null, "plugin_id": 156899}</t>
         </is>
       </c>
     </row>
@@ -19489,16 +16973,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -19522,11 +16998,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
           <t>['Nessus was able to identify the remote service by its banner or by looking at the error message it sends when it receives an HTTP request.']</t>
@@ -19542,7 +17014,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{"plugin_id": 22964, "publication_date": "2007/08/19", "modification_date": "2026/03/23"}</t>
+          <t>{"publication_date": "2007/08/19", "modification_date": "2026/03/23", "family": null, "severity": null, "plugin_id": 22964}</t>
         </is>
       </c>
     </row>
@@ -19562,11 +17034,7 @@
           <t>['Replace affected ciphers with algorithms chosen to resist CRQC attack.']</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>['http://www.nessus.org/u?54fba2c1']</t>
@@ -19595,11 +17063,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
           <t>["This plugin reports network services that may be vulnerable now to a future attack by adversaries using a cryptographically relevant quantum computer (CRQC). Shor's is a theoretical algorithm that leverages the unique ability of quantum computation to do massively parallel calculations developed by Peter Shor in 1994.", "This algorithm easily computes two classically difficult mathematical problems used in modern cryptography; discrete logarithms, and factoring numbers formed by multiplying large primes.  Shor's reduces both of these problems from taking exponential time in chosen cases to being solvable in polynomial time.", "Asymmetric encryption algorithms such as RSA, Diffie-Hellman and Elliptic Curve Diffie-Hellman are impacted by Shor's Algorithm.  The most common uses of these algorithms are in symmetric key establishment and authentication.  These uses render Shor's Algorithm particularly dangerous because it may give an adversary the ability to harvest network communications now, and in the future, when a CRQC becomes available, extract the symmetric key and decrypt the communication."]</t>
@@ -19615,7 +17079,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{"plugin_id": 298387, "publication_date": "2026/02/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2026/02/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 298387}</t>
         </is>
       </c>
     </row>
@@ -19635,11 +17099,7 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>['http://www.ietf.org/rfc/rfc1323.txt']</t>
@@ -19668,27 +17128,19 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>['The remote host implements TCP timestamps, as defined by RFC1323.  A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="n">
         <v>25220</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{"plugin_id": 25220, "publication_date": "2007/05/16", "modification_date": "2023/10/17"}</t>
+          <t>{"publication_date": "2007/05/16", "modification_date": "2023/10/17", "family": null, "severity": null, "plugin_id": 25220}</t>
         </is>
       </c>
     </row>
@@ -19708,16 +17160,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -19741,11 +17185,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>['This plugin detects which TLS supported groups entries are supported by the remote service.']</t>
@@ -19761,7 +17201,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>{"plugin_id": 277654, "publication_date": "2025/12/08", "modification_date": "2026/06/15"}</t>
+          <t>{"publication_date": "2025/12/08", "modification_date": "2026/06/15", "family": null, "severity": null, "plugin_id": 277654}</t>
         </is>
       </c>
     </row>
@@ -19781,11 +17221,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc5246']</t>
@@ -19814,11 +17250,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.2.']</t>
@@ -19834,7 +17266,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>{"plugin_id": 136318, "publication_date": "2020/05/04", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/05/04", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 136318}</t>
         </is>
       </c>
     </row>
@@ -19854,11 +17286,7 @@
           <t>['N/A']</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>['https://tools.ietf.org/html/rfc8446']</t>
@@ -19887,11 +17315,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>['The remote service accepts connections encrypted using TLS 1.3.']</t>
@@ -19907,7 +17331,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>{"plugin_id": 138330, "publication_date": "2020/07/09", "modification_date": "2026/04/13"}</t>
+          <t>{"publication_date": "2020/07/09", "modification_date": "2026/04/13", "family": null, "severity": null, "plugin_id": 138330}</t>
         </is>
       </c>
     </row>
@@ -19927,16 +17351,8 @@
           <t>['n/a']</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -19960,11 +17376,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>['Makes a traceroute to the remote host.']</t>
@@ -19980,7 +17392,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10287, "publication_date": "1999/11/27", "modification_date": "2026/04/27"}</t>
+          <t>{"publication_date": "1999/11/27", "modification_date": "2026/04/27", "family": null, "severity": null, "plugin_id": 10287}</t>
         </is>
       </c>
     </row>
@@ -20000,11 +17412,7 @@
           <t>["Stop the Webmin service if not needed or ensure access is limited to authorized hosts. See the menu items '[Webmin Configuration][IP Access Control]' and/or '[Webmin Configuration][Port and Address]'."]</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>['http://www.webmin.com/']</t>
@@ -20033,11 +17441,7 @@
           <t>NESSUS</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>['The remote web server is running Webmin, a web-based interface for system administration for Unix.']</t>
@@ -20053,7 +17457,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>{"plugin_id": 10757, "publication_date": "2001/09/14", "modification_date": "2023/05/24"}</t>
+          <t>{"publication_date": "2001/09/14", "modification_date": "2023/05/24", "family": null, "severity": null, "plugin_id": 10757}</t>
         </is>
       </c>
     </row>
